--- a/Results/Phase 2/Carbon dioxide/carbon dioxide resource use fossils results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide resource use fossils results.xlsx
@@ -2098,7 +2098,7 @@
         <v>3.180716984534018</v>
       </c>
       <c r="N2" t="n">
-        <v>4.946517093373817</v>
+        <v>4.946517093373818</v>
       </c>
       <c r="O2" t="n">
         <v>5.243654751552537</v>
@@ -2948,7 +2948,7 @@
         <v>8.742415682399621</v>
       </c>
       <c r="D12" t="n">
-        <v>9.088631832268065</v>
+        <v>9.088631832268067</v>
       </c>
       <c r="E12" t="n">
         <v>8.60755922033937</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.881553203487239</v>
+        <v>4.881553203487216</v>
       </c>
       <c r="C2" t="n">
         <v>3.164121933695938</v>
       </c>
       <c r="D2" t="n">
-        <v>6.508360996310419</v>
+        <v>6.508360996310387</v>
       </c>
       <c r="E2" t="n">
-        <v>4.099216325343752</v>
+        <v>4.099216325343753</v>
       </c>
       <c r="F2" t="n">
-        <v>4.592942467843787</v>
+        <v>4.592942467843788</v>
       </c>
       <c r="G2" t="n">
-        <v>7.683985716794901</v>
+        <v>7.683985716794881</v>
       </c>
       <c r="H2" t="n">
-        <v>6.873528043203862</v>
+        <v>6.873528043203846</v>
       </c>
       <c r="I2" t="n">
-        <v>4.846471307448293</v>
+        <v>4.846471307448262</v>
       </c>
       <c r="J2" t="n">
-        <v>7.777993706817877</v>
+        <v>7.77799370681782</v>
       </c>
       <c r="K2" t="n">
-        <v>5.072061771755806</v>
+        <v>5.072061771755769</v>
       </c>
       <c r="L2" t="n">
-        <v>8.001820162268672</v>
+        <v>8.001820162268599</v>
       </c>
       <c r="M2" t="n">
-        <v>11.72392600212417</v>
+        <v>11.72392600212416</v>
       </c>
       <c r="N2" t="n">
-        <v>7.044040618155618</v>
+        <v>7.044040618155595</v>
       </c>
       <c r="O2" t="n">
-        <v>8.054425182805558</v>
+        <v>8.054425182805542</v>
       </c>
       <c r="P2" t="n">
-        <v>10.40787461044073</v>
+        <v>10.40787461044072</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.615067190059347</v>
+        <v>5.615067190059315</v>
       </c>
       <c r="R2" t="n">
-        <v>5.365466095898386</v>
+        <v>5.365466095898353</v>
       </c>
       <c r="S2" t="n">
-        <v>7.108983474642409</v>
+        <v>7.108983474642389</v>
       </c>
       <c r="T2" t="n">
-        <v>6.581572300225333</v>
+        <v>6.581572300225282</v>
       </c>
       <c r="U2" t="n">
-        <v>8.791907319236925</v>
+        <v>8.791907319236888</v>
       </c>
       <c r="V2" t="n">
-        <v>6.743441737754329</v>
+        <v>6.743441737754324</v>
       </c>
       <c r="W2" t="n">
-        <v>11.60605508169304</v>
+        <v>11.60605508169302</v>
       </c>
       <c r="X2" t="n">
-        <v>8.358948775242251</v>
+        <v>8.35894877524221</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.70871419039364</v>
+        <v>12.70871419039362</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.805855125559377</v>
+        <v>6.805855125559336</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.355811215328963</v>
+        <v>6.35581121532892</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.94294753134518</v>
+        <v>12.94294753134516</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4479726512710842</v>
+        <v>0.4479726512710538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5560385171209238</v>
+        <v>0.5560385171209242</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4798770161918227</v>
+        <v>0.4798770161918235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4526618846269844</v>
+        <v>0.4526618846269843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5963374217291396</v>
+        <v>0.5963374217291605</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="J3" t="n">
-        <v>0.561641041564881</v>
+        <v>0.5616410415648648</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5733979438315727</v>
+        <v>0.5733979438315732</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4756009880728633</v>
+        <v>0.4756009880728523</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5017780650789021</v>
+        <v>0.5017780650789058</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4953614309867869</v>
+        <v>0.4953614309868073</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4238231450925459</v>
+        <v>0.4238231450925096</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5106475598601831</v>
+        <v>0.5106475598601712</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5140753682173498</v>
+        <v>0.5140753682173425</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5708807785982274</v>
+        <v>0.5708807785981993</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4350857056822111</v>
+        <v>0.4350857056821892</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6926421288955853</v>
+        <v>0.6926421288955765</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4456900183191524</v>
+        <v>0.445690018319146</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5708566285402211</v>
+        <v>0.5708566285402243</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7147490223486772</v>
+        <v>0.7147490223486774</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.35242069357296</v>
+        <v>11.35242069357281</v>
       </c>
       <c r="C4" t="n">
-        <v>10.71702007902034</v>
+        <v>10.7170200790202</v>
       </c>
       <c r="D4" t="n">
-        <v>11.94537303111545</v>
+        <v>11.9453730311152</v>
       </c>
       <c r="E4" t="n">
-        <v>11.05103233962051</v>
+        <v>11.05103233962049</v>
       </c>
       <c r="F4" t="n">
-        <v>11.2380393670484</v>
+        <v>11.23803936704822</v>
       </c>
       <c r="G4" t="n">
-        <v>12.37387443684959</v>
+        <v>12.37387443684938</v>
       </c>
       <c r="H4" t="n">
-        <v>12.07847213170008</v>
+        <v>12.0784721317</v>
       </c>
       <c r="I4" t="n">
-        <v>11.33963375441919</v>
+        <v>11.33963375441896</v>
       </c>
       <c r="J4" t="n">
-        <v>12.4232238982241</v>
+        <v>12.42322389822386</v>
       </c>
       <c r="K4" t="n">
-        <v>11.42185882964231</v>
+        <v>11.42185882964217</v>
       </c>
       <c r="L4" t="n">
-        <v>12.48972136002441</v>
+        <v>12.48972136002406</v>
       </c>
       <c r="M4" t="n">
-        <v>13.84800026718743</v>
+        <v>13.84800026718707</v>
       </c>
       <c r="N4" t="n">
-        <v>12.14062196301027</v>
+        <v>12.14062196301012</v>
       </c>
       <c r="O4" t="n">
-        <v>12.50889527229058</v>
+        <v>12.5088952722905</v>
       </c>
       <c r="P4" t="n">
-        <v>13.36669995306517</v>
+        <v>13.36669995306493</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.61977792832246</v>
+        <v>11.61977792832218</v>
       </c>
       <c r="R4" t="n">
-        <v>11.52880126046475</v>
+        <v>11.52880126046451</v>
       </c>
       <c r="S4" t="n">
-        <v>12.16429287160221</v>
+        <v>12.16429287160187</v>
       </c>
       <c r="T4" t="n">
-        <v>11.97205769170194</v>
+        <v>11.97205769170166</v>
       </c>
       <c r="U4" t="n">
-        <v>12.77769885106755</v>
+        <v>12.77769885106741</v>
       </c>
       <c r="V4" t="n">
-        <v>12.15619435502535</v>
+        <v>12.15619435502536</v>
       </c>
       <c r="W4" t="n">
-        <v>13.80342266509122</v>
+        <v>13.803422665091</v>
       </c>
       <c r="X4" t="n">
-        <v>12.61989054583722</v>
+        <v>12.6198905458372</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.20532896213565</v>
+        <v>14.20532896213546</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.05380614787424</v>
+        <v>12.05380614787397</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.88977042727766</v>
+        <v>11.8897704272774</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.30057363740724</v>
+        <v>14.30057363740681</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.736432644021223</v>
+        <v>9.736432644021219</v>
       </c>
       <c r="C5" t="n">
-        <v>9.766404299340456</v>
+        <v>9.766404299340223</v>
       </c>
       <c r="D5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="E5" t="n">
-        <v>9.731825661862551</v>
+        <v>9.731825661862652</v>
       </c>
       <c r="F5" t="n">
-        <v>9.728955712095351</v>
+        <v>9.728955712094827</v>
       </c>
       <c r="G5" t="n">
-        <v>9.79050986066637</v>
+        <v>9.790509860666242</v>
       </c>
       <c r="H5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="I5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="J5" t="n">
-        <v>9.792948090430347</v>
+        <v>9.792948090430333</v>
       </c>
       <c r="K5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="L5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="M5" t="n">
-        <v>9.78376372605099</v>
+        <v>9.783763726050662</v>
       </c>
       <c r="N5" t="n">
-        <v>9.746502848357562</v>
+        <v>9.746502848357299</v>
       </c>
       <c r="O5" t="n">
-        <v>9.756044085539509</v>
+        <v>9.756044085539243</v>
       </c>
       <c r="P5" t="n">
-        <v>9.753705297760728</v>
+        <v>9.753705297760517</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.727630432597255</v>
+        <v>9.727630432596944</v>
       </c>
       <c r="R5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="S5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="T5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="U5" t="n">
-        <v>9.759276912236222</v>
+        <v>9.759276912236251</v>
       </c>
       <c r="V5" t="n">
-        <v>9.885663462242192</v>
+        <v>9.885663462242237</v>
       </c>
       <c r="W5" t="n">
-        <v>9.781231213172259</v>
+        <v>9.781231213171928</v>
       </c>
       <c r="X5" t="n">
-        <v>9.731735503680557</v>
+        <v>9.731735503680246</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.825611795561517</v>
+        <v>9.825611795561331</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.735600651114776</v>
+        <v>9.735600651114337</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.781222410759685</v>
+        <v>9.781222410759383</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.843538871634205</v>
+        <v>9.843538871634232</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.94983552768343</v>
+        <v>1.949835527683415</v>
       </c>
       <c r="C6" t="n">
-        <v>1.31443491313064</v>
+        <v>1.314434913130642</v>
       </c>
       <c r="D6" t="n">
-        <v>2.54278786522591</v>
+        <v>2.542787865225893</v>
       </c>
       <c r="E6" t="n">
-        <v>1.648447173731105</v>
+        <v>1.648447173731108</v>
       </c>
       <c r="F6" t="n">
-        <v>1.835454201158786</v>
+        <v>1.835454201158787</v>
       </c>
       <c r="G6" t="n">
-        <v>2.962506619267831</v>
+        <v>2.962506619267798</v>
       </c>
       <c r="H6" t="n">
-        <v>2.675886965810612</v>
+        <v>2.675886965810597</v>
       </c>
       <c r="I6" t="n">
-        <v>1.93704858852966</v>
+        <v>1.937048588529637</v>
       </c>
       <c r="J6" t="n">
-        <v>2.991240386463313</v>
+        <v>2.991240386463294</v>
       </c>
       <c r="K6" t="n">
-        <v>2.019273663752771</v>
+        <v>2.019273663752749</v>
       </c>
       <c r="L6" t="n">
-        <v>3.087136194134758</v>
+        <v>3.087136194134724</v>
       </c>
       <c r="M6" t="n">
-        <v>4.445415101297748</v>
+        <v>4.445415101297737</v>
       </c>
       <c r="N6" t="n">
-        <v>2.738036797120781</v>
+        <v>2.738036797120763</v>
       </c>
       <c r="O6" t="n">
-        <v>3.097527454708871</v>
+        <v>3.097527454708854</v>
       </c>
       <c r="P6" t="n">
-        <v>3.955332135483443</v>
+        <v>3.955332135483421</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.217192762432864</v>
+        <v>2.217192762432842</v>
       </c>
       <c r="R6" t="n">
-        <v>2.126216094575218</v>
+        <v>2.126216094575199</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7617077057127</v>
+        <v>2.761707705712676</v>
       </c>
       <c r="T6" t="n">
-        <v>2.569472525812362</v>
+        <v>2.569472525812341</v>
       </c>
       <c r="U6" t="n">
-        <v>3.366331033485638</v>
+        <v>3.366331033485626</v>
       </c>
       <c r="V6" t="n">
-        <v>2.605586880441494</v>
+        <v>2.605586880441504</v>
       </c>
       <c r="W6" t="n">
-        <v>4.392054847509474</v>
+        <v>4.392054847509454</v>
       </c>
       <c r="X6" t="n">
-        <v>3.208522728255485</v>
+        <v>3.208522728255465</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.802743796246112</v>
+        <v>4.80274379624609</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.651220981984719</v>
+        <v>2.651220981984693</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.487185261388136</v>
+        <v>2.487185261388117</v>
       </c>
       <c r="AB6" t="n">
         <v>4.897988471517499</v>
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3338474781319713</v>
+        <v>0.3338474781319508</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3638191334507486</v>
+        <v>0.3638191334507494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3292404959731509</v>
+        <v>0.329240495973151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3263705462054701</v>
+        <v>0.3263705462054702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3791420430845799</v>
+        <v>0.3791420430845971</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3609645786698826</v>
+        <v>0.3609645786698557</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.3786372448700481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3811785601612333</v>
+        <v>0.381178560161233</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3439176824679164</v>
+        <v>0.3439176824678925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3446762679576252</v>
+        <v>0.3446762679576026</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3423374801789794</v>
+        <v>0.3423374801789548</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3250452667076872</v>
+        <v>0.3250452667076921</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.3786372448700481</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.3786372448700481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3479090946545063</v>
+        <v>0.3479090946545091</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3350559876583083</v>
+        <v>0.3350559876583097</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3698633955903641</v>
+        <v>0.3698633955903562</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3203676860987595</v>
+        <v>0.3203676860987234</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4230266296720075</v>
+        <v>0.4230266296720286</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3330154852250331</v>
+        <v>0.3330154852250066</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3786372448700423</v>
+        <v>0.378637244870048</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.440953705744759</v>
+        <v>0.4409537057447592</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="C8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="D8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="E8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="F8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="G8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="H8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="I8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="J8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="K8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="L8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="M8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="N8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="O8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="P8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="R8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="S8" t="n">
-        <v>1.163479264533692</v>
+        <v>1.163479264533693</v>
       </c>
       <c r="T8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="U8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="V8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="W8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="X8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.167150825421147</v>
+        <v>1.167150825421148</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.42581845615253</v>
+        <v>5.425818456152515</v>
       </c>
       <c r="C9" t="n">
         <v>3.596015004298565</v>
       </c>
       <c r="D9" t="n">
-        <v>7.174153655004818</v>
+        <v>7.174153655004832</v>
       </c>
       <c r="E9" t="n">
-        <v>4.612494669558824</v>
+        <v>4.61249466955883</v>
       </c>
       <c r="F9" t="n">
-        <v>5.131182095642222</v>
+        <v>5.131182095642221</v>
       </c>
       <c r="G9" t="n">
-        <v>8.437601057046697</v>
+        <v>8.437601057046702</v>
       </c>
       <c r="H9" t="n">
-        <v>7.566599772094548</v>
+        <v>7.566599772094549</v>
       </c>
       <c r="I9" t="n">
         <v>5.388115837589999</v>
       </c>
       <c r="J9" t="n">
-        <v>8.548535743869417</v>
+        <v>8.548535743869406</v>
       </c>
       <c r="K9" t="n">
-        <v>5.630558584062091</v>
+        <v>5.630558584062092</v>
       </c>
       <c r="L9" t="n">
-        <v>8.779178685873481</v>
+        <v>8.779178685873466</v>
       </c>
       <c r="M9" t="n">
-        <v>12.77660580134901</v>
+        <v>12.776605801349</v>
       </c>
       <c r="N9" t="n">
-        <v>7.749850146201595</v>
+        <v>7.749850146201587</v>
       </c>
       <c r="O9" t="n">
-        <v>8.835713458725396</v>
+        <v>8.835713458725408</v>
       </c>
       <c r="P9" t="n">
-        <v>11.36497259505691</v>
+        <v>11.36497259505689</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.214128130615629</v>
+        <v>6.214128130615631</v>
       </c>
       <c r="R9" t="n">
-        <v>5.945881088451949</v>
+        <v>5.945881088451943</v>
       </c>
       <c r="S9" t="n">
         <v>7.81964442823709</v>
       </c>
       <c r="T9" t="n">
-        <v>7.252834062212724</v>
+        <v>7.252834062212703</v>
       </c>
       <c r="U9" t="n">
-        <v>9.628287715706408</v>
+        <v>9.628287715706431</v>
       </c>
       <c r="V9" t="n">
-        <v>7.451449732849063</v>
+        <v>7.451449732849081</v>
       </c>
       <c r="W9" t="n">
-        <v>12.6526607298872</v>
+        <v>12.65266072988717</v>
       </c>
       <c r="X9" t="n">
-        <v>9.162985873995829</v>
+        <v>9.162985873995824</v>
       </c>
       <c r="Y9" t="n">
         <v>13.83769177078897</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.49387148517039</v>
+        <v>7.493871485170386</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.01020794928365</v>
+        <v>7.010207949283642</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.07273311550396</v>
+        <v>14.07273311550394</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6610361809615313</v>
+        <v>0.661036180961532</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7227798927450984</v>
+        <v>0.7227798927450986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6816101740566453</v>
+        <v>0.6816101740566464</v>
       </c>
       <c r="G10" t="n">
-        <v>0.820484243360714</v>
+        <v>0.8204842433607143</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7930999587371862</v>
+        <v>0.7930999587371865</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6907284371269043</v>
+        <v>0.6907284371269053</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7188610200507461</v>
+        <v>0.7188610200507457</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7119650442072165</v>
+        <v>0.7119650442072176</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6350826344681394</v>
+        <v>0.6350826344681396</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7283930926105965</v>
+        <v>0.7283930926105977</v>
       </c>
       <c r="V10" t="n">
-        <v>0.756731070659846</v>
+        <v>0.7567310706598468</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7931259128764198</v>
+        <v>0.7931259128764205</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6471865420071907</v>
+        <v>0.6471865420071913</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9239832000887285</v>
+        <v>0.9239832000887288</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6585830285033931</v>
+        <v>0.6585830285033937</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7930999587369072</v>
+        <v>0.7930999587369081</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9310516174516681</v>
+        <v>0.9310516174516684</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="C11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="D11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="E11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="F11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="G11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="H11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="I11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="J11" t="n">
-        <v>8.914703243012335</v>
+        <v>8.914703243011823</v>
       </c>
       <c r="K11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="L11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="M11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="N11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="O11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="P11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="R11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="S11" t="n">
-        <v>8.894891959483122</v>
+        <v>8.894891959482841</v>
       </c>
       <c r="T11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="U11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="V11" t="n">
-        <v>9.016834618664175</v>
+        <v>9.016834618664134</v>
       </c>
       <c r="W11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="X11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.896696625040589</v>
+        <v>8.896696625040013</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.98994007904984</v>
+        <v>10.98994007904976</v>
       </c>
       <c r="C12" t="n">
-        <v>10.09054514386467</v>
+        <v>10.09054514386439</v>
       </c>
       <c r="D12" t="n">
-        <v>11.84929129584883</v>
+        <v>11.84929129584861</v>
       </c>
       <c r="E12" t="n">
-        <v>10.59017075213839</v>
+        <v>10.59017075213798</v>
       </c>
       <c r="F12" t="n">
-        <v>10.84511881417774</v>
+        <v>10.84511881417783</v>
       </c>
       <c r="G12" t="n">
-        <v>12.47030782804419</v>
+        <v>12.47030782804414</v>
       </c>
       <c r="H12" t="n">
-        <v>12.0421885437396</v>
+        <v>12.04218854373921</v>
       </c>
       <c r="I12" t="n">
-        <v>10.97140828311075</v>
+        <v>10.97140828311054</v>
       </c>
       <c r="J12" t="n">
-        <v>12.54284166606406</v>
+        <v>12.5428416660638</v>
       </c>
       <c r="K12" t="n">
-        <v>11.09057505920824</v>
+        <v>11.0905750592081</v>
       </c>
       <c r="L12" t="n">
-        <v>12.63820192018184</v>
+        <v>12.63820192018171</v>
       </c>
       <c r="M12" t="n">
-        <v>14.60303901664048</v>
+        <v>14.6030390166401</v>
       </c>
       <c r="N12" t="n">
-        <v>12.13226076334094</v>
+        <v>12.13226076334074</v>
       </c>
       <c r="O12" t="n">
-        <v>12.66599019892481</v>
+        <v>12.66599019892452</v>
       </c>
       <c r="P12" t="n">
-        <v>13.90918539274888</v>
+        <v>13.90918539274854</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.37741433364864</v>
+        <v>11.37741433364853</v>
       </c>
       <c r="R12" t="n">
-        <v>11.24556408992126</v>
+        <v>11.24556408992099</v>
       </c>
       <c r="S12" t="n">
-        <v>12.16656642808546</v>
+        <v>12.16656642808533</v>
       </c>
       <c r="T12" t="n">
-        <v>11.88796471712233</v>
+        <v>11.88796471712204</v>
       </c>
       <c r="U12" t="n">
-        <v>13.05556060429513</v>
+        <v>13.05556060429478</v>
       </c>
       <c r="V12" t="n">
-        <v>12.10572736438716</v>
+        <v>12.1057273643872</v>
       </c>
       <c r="W12" t="n">
-        <v>14.54211686164024</v>
+        <v>14.54211686163996</v>
       </c>
       <c r="X12" t="n">
-        <v>12.82685291476553</v>
+        <v>12.82685291476536</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.12458975792006</v>
+        <v>15.12458975791981</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.00644074096991</v>
+        <v>12.00644074096972</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.76870781174753</v>
+        <v>11.76870781174739</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.24011855680915</v>
+        <v>15.24011855680896</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.647928404940815</v>
+        <v>8.647928404940364</v>
       </c>
       <c r="C13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="D13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="E13" t="n">
-        <v>8.678277009651078</v>
+        <v>8.678277009650799</v>
       </c>
       <c r="F13" t="n">
-        <v>8.658041045818869</v>
+        <v>8.658041045818855</v>
       </c>
       <c r="G13" t="n">
-        <v>8.726301182957782</v>
+        <v>8.726301182957526</v>
       </c>
       <c r="H13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="I13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="J13" t="n">
-        <v>8.730847728554318</v>
+        <v>8.73084772855403</v>
       </c>
       <c r="K13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="L13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="M13" t="n">
-        <v>8.712841110582735</v>
+        <v>8.712841110582254</v>
       </c>
       <c r="N13" t="n">
-        <v>8.662522904028778</v>
+        <v>8.662522904028418</v>
       </c>
       <c r="O13" t="n">
-        <v>8.676350784050396</v>
+        <v>8.676350784050335</v>
       </c>
       <c r="P13" t="n">
-        <v>8.672961236533384</v>
+        <v>8.672961236532997</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.635171576745508</v>
+        <v>8.635171576745533</v>
       </c>
       <c r="R13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="S13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="T13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="U13" t="n">
-        <v>8.681036040148989</v>
+        <v>8.68103604014903</v>
       </c>
       <c r="V13" t="n">
-        <v>8.815102870722461</v>
+        <v>8.815102870722427</v>
       </c>
       <c r="W13" t="n">
-        <v>8.712853867702238</v>
+        <v>8.712853867702</v>
       </c>
       <c r="X13" t="n">
-        <v>8.641120955147876</v>
+        <v>8.6411209551475</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.777173552546806</v>
+        <v>8.77717355254682</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.646722618114753</v>
+        <v>8.646722618114559</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.7128411105826</v>
+        <v>8.712841110582106</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.780647859456446</v>
+        <v>8.780647859456392</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8041193297236869</v>
+        <v>0.8041193297236872</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="J14" t="n">
-        <v>0.804399280566729</v>
+        <v>0.8043992805667294</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8041193297236869</v>
+        <v>0.8041193297236872</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8041193297236869</v>
+        <v>0.8041193297236872</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8098666256935351</v>
+        <v>0.8098666256935355</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8041193297236868</v>
+        <v>0.8041193297236874</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8045289577485137</v>
+        <v>0.8045289577485139</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8041193297236869</v>
+        <v>0.8041193297236872</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8041193297236869</v>
+        <v>0.8041193297236872</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8116712912509512</v>
+        <v>0.8116712912509518</v>
       </c>
     </row>
     <row r="15">
@@ -6158,73 +6158,73 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.904914745260287</v>
+        <v>2.904914745260289</v>
       </c>
       <c r="C15" t="n">
-        <v>2.005519810075074</v>
+        <v>2.005519810075077</v>
       </c>
       <c r="D15" t="n">
-        <v>3.76426596205932</v>
+        <v>3.764265962059321</v>
       </c>
       <c r="E15" t="n">
-        <v>2.505145418348767</v>
+        <v>2.50514541834877</v>
       </c>
       <c r="F15" t="n">
-        <v>2.760093480388432</v>
+        <v>2.760093480388431</v>
       </c>
       <c r="G15" t="n">
-        <v>4.377730532727381</v>
+        <v>4.377730532727372</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95716320995005</v>
+        <v>3.957163209950057</v>
       </c>
       <c r="I15" t="n">
-        <v>2.886382949321216</v>
+        <v>2.886382949321218</v>
       </c>
       <c r="J15" t="n">
-        <v>4.432537703618902</v>
+        <v>4.43253770361889</v>
       </c>
       <c r="K15" t="n">
-        <v>3.005549725418653</v>
+        <v>3.005549725418651</v>
       </c>
       <c r="L15" t="n">
-        <v>4.553176586392301</v>
+        <v>4.553176586392278</v>
       </c>
       <c r="M15" t="n">
-        <v>6.518013682850926</v>
+        <v>6.518013682850921</v>
       </c>
       <c r="N15" t="n">
-        <v>4.04723542955139</v>
+        <v>4.047235429551383</v>
       </c>
       <c r="O15" t="n">
-        <v>4.573412903607945</v>
+        <v>4.573412903607954</v>
       </c>
       <c r="P15" t="n">
-        <v>5.81660809743198</v>
+        <v>5.816608097431988</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.292388999859189</v>
+        <v>3.292388999859188</v>
       </c>
       <c r="R15" t="n">
-        <v>3.160538756131654</v>
+        <v>3.160538756131648</v>
       </c>
       <c r="S15" t="n">
-        <v>4.081541094295881</v>
+        <v>4.081541094295878</v>
       </c>
       <c r="T15" t="n">
-        <v>3.802939383332735</v>
+        <v>3.802939383332727</v>
       </c>
       <c r="U15" t="n">
-        <v>4.962983308978344</v>
+        <v>4.962983308978342</v>
       </c>
       <c r="V15" t="n">
-        <v>3.893421703471513</v>
+        <v>3.893421703471514</v>
       </c>
       <c r="W15" t="n">
-        <v>6.449539566323358</v>
+        <v>6.449539566323363</v>
       </c>
       <c r="X15" t="n">
-        <v>4.734275619448725</v>
+        <v>4.734275619448726</v>
       </c>
       <c r="Y15" t="n">
         <v>7.039564424130512</v>
@@ -6233,10 +6233,10 @@
         <v>3.921415407180304</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.683682477958018</v>
+        <v>3.683682477958014</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.15509322301959</v>
+        <v>7.155093223019585</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5629030711512275</v>
+        <v>0.562903071151228</v>
       </c>
       <c r="C16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="D16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5932516758614278</v>
+        <v>0.5932516758614281</v>
       </c>
       <c r="F16" t="n">
-        <v>0.573015712029423</v>
+        <v>0.5730157120294231</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6337238876409794</v>
+        <v>0.6337238876409796</v>
       </c>
       <c r="H16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="I16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6205437661088342</v>
+        <v>0.6205437661088347</v>
       </c>
       <c r="K16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="L16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6278157767931929</v>
+        <v>0.6278157767931933</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5774975702392585</v>
+        <v>0.5774975702392592</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5837734887336131</v>
+        <v>0.5837734887336137</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5803839412166133</v>
+        <v>0.5803839412166134</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5501462429560465</v>
+        <v>0.5501462429560466</v>
       </c>
       <c r="R16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="S16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="T16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5884587448322731</v>
+        <v>0.5884587448322736</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6027972098068064</v>
+        <v>0.6027972098068067</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6202765723854713</v>
+        <v>0.6202765723854715</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5485436598308959</v>
+        <v>0.548543659830896</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6921482187573454</v>
+        <v>0.692148218757346</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.5616972843254069</v>
+        <v>0.5616972843254072</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.627815776793056</v>
+        <v>0.6278157767930563</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6956225256669544</v>
+        <v>0.6956225256669549</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.526506404365885</v>
+        <v>4.526506404365882</v>
       </c>
       <c r="C2" t="n">
-        <v>3.314593860909164</v>
+        <v>3.314593860909163</v>
       </c>
       <c r="D2" t="n">
-        <v>5.06318463848557</v>
+        <v>5.063184638485549</v>
       </c>
       <c r="E2" t="n">
-        <v>2.364168832517624</v>
+        <v>2.364168832517628</v>
       </c>
       <c r="F2" t="n">
-        <v>5.859781575752889</v>
+        <v>5.85978157575288</v>
       </c>
       <c r="G2" t="n">
-        <v>7.11009407872451</v>
+        <v>7.110094078724474</v>
       </c>
       <c r="H2" t="n">
-        <v>6.388905766023839</v>
+        <v>6.388905766023848</v>
       </c>
       <c r="I2" t="n">
-        <v>5.797596833397125</v>
+        <v>5.797596833397124</v>
       </c>
       <c r="J2" t="n">
-        <v>7.2722494032405</v>
+        <v>7.272249403240482</v>
       </c>
       <c r="K2" t="n">
         <v>6.908855262737102</v>
       </c>
       <c r="L2" t="n">
-        <v>8.120881044235544</v>
+        <v>8.120881044235501</v>
       </c>
       <c r="M2" t="n">
-        <v>10.74960675053979</v>
+        <v>10.74960675053977</v>
       </c>
       <c r="N2" t="n">
-        <v>6.247805158847616</v>
+        <v>6.24780515884762</v>
       </c>
       <c r="O2" t="n">
-        <v>6.60001155365795</v>
+        <v>6.600011553657936</v>
       </c>
       <c r="P2" t="n">
-        <v>9.298989542704508</v>
+        <v>9.298989542704506</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.199164096140477</v>
+        <v>6.199164096140471</v>
       </c>
       <c r="R2" t="n">
-        <v>5.699760160444639</v>
+        <v>5.69976016044463</v>
       </c>
       <c r="S2" t="n">
-        <v>7.533436293022207</v>
+        <v>7.533436293022204</v>
       </c>
       <c r="T2" t="n">
-        <v>6.939079483347108</v>
+        <v>6.939079483347102</v>
       </c>
       <c r="U2" t="n">
-        <v>8.314235536454516</v>
+        <v>8.314235536454497</v>
       </c>
       <c r="V2" t="n">
-        <v>6.240664720825131</v>
+        <v>6.240664720825122</v>
       </c>
       <c r="W2" t="n">
-        <v>10.95771152264164</v>
+        <v>10.95771152264163</v>
       </c>
       <c r="X2" t="n">
         <v>8.770992774129883</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.56144580525046</v>
+        <v>11.56144580525042</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.099833417800132</v>
+        <v>5.099833417800131</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.909274555941661</v>
+        <v>6.909274555941656</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.79702462852516</v>
+        <v>11.79702462852515</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4185926293767908</v>
+        <v>0.4185926293767683</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5238795500517908</v>
+        <v>0.5238795500517905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4486079650747244</v>
+        <v>0.4486079650747237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4311065143029271</v>
+        <v>0.4311065143029267</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5583101147389481</v>
+        <v>0.5583101147389655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5268276877581977</v>
+        <v>0.526827687758203</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5385764510674309</v>
+        <v>0.5385764510674305</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4446106775362748</v>
+        <v>0.4446106775362551</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4692620510570567</v>
+        <v>0.4692620510570513</v>
       </c>
       <c r="P3" t="n">
-        <v>0.463219403754344</v>
+        <v>0.4632194037543488</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3958506518447187</v>
+        <v>0.3958506518447207</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4771367583813783</v>
+        <v>0.4771367583813864</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4828983971562181</v>
+        <v>0.4828983971562035</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5343371853702471</v>
+        <v>0.5343371853702457</v>
       </c>
       <c r="X3" t="n">
-        <v>0.406456785902937</v>
+        <v>0.4064567859029277</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6481843607947736</v>
+        <v>0.6481843607947841</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4164430372925454</v>
+        <v>0.4164430372925603</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5343144428657131</v>
+        <v>0.5343144428657087</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6712860997814497</v>
+        <v>0.6712860997814494</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.13898958207213</v>
+        <v>11.13898958207249</v>
       </c>
       <c r="C4" t="n">
-        <v>10.6906301940618</v>
+        <v>10.69063019406206</v>
       </c>
       <c r="D4" t="n">
-        <v>11.33460249641476</v>
+        <v>11.33460249641479</v>
       </c>
       <c r="E4" t="n">
-        <v>10.33553470538353</v>
+        <v>10.33553470538379</v>
       </c>
       <c r="F4" t="n">
-        <v>11.62144837365644</v>
+        <v>11.62144837365662</v>
       </c>
       <c r="G4" t="n">
-        <v>12.08067695135767</v>
+        <v>12.08067695135778</v>
       </c>
       <c r="H4" t="n">
-        <v>11.81781227999902</v>
+        <v>11.81781227999918</v>
       </c>
       <c r="I4" t="n">
-        <v>11.60228711755663</v>
+        <v>11.60228711755682</v>
       </c>
       <c r="J4" t="n">
-        <v>12.15828419909309</v>
+        <v>12.15828419909331</v>
       </c>
       <c r="K4" t="n">
-        <v>12.00732776599575</v>
+        <v>12.0073277659959</v>
       </c>
       <c r="L4" t="n">
-        <v>12.44909693102666</v>
+        <v>12.44909693102673</v>
       </c>
       <c r="M4" t="n">
-        <v>13.40994513917786</v>
+        <v>13.40994513917803</v>
       </c>
       <c r="N4" t="n">
-        <v>11.76638276557028</v>
+        <v>11.76638276557037</v>
       </c>
       <c r="O4" t="n">
-        <v>11.89475786066234</v>
+        <v>11.89475786066233</v>
       </c>
       <c r="P4" t="n">
-        <v>12.87850364467016</v>
+        <v>12.87850364467021</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.74865366938571</v>
+        <v>11.7486536693858</v>
       </c>
       <c r="R4" t="n">
-        <v>11.56662679912166</v>
+        <v>11.56662679912187</v>
       </c>
       <c r="S4" t="n">
-        <v>12.23498021733393</v>
+        <v>12.23498021733399</v>
       </c>
       <c r="T4" t="n">
-        <v>12.01834413949739</v>
+        <v>12.0183441394975</v>
       </c>
       <c r="U4" t="n">
-        <v>12.51957237295738</v>
+        <v>12.51957237295745</v>
       </c>
       <c r="V4" t="n">
         <v>11.90688815583283</v>
       </c>
       <c r="W4" t="n">
-        <v>13.48308832866035</v>
+        <v>13.48308832866055</v>
       </c>
       <c r="X4" t="n">
-        <v>12.68605502257578</v>
+        <v>12.68605502257584</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.7031423852654</v>
+        <v>13.70314238526549</v>
       </c>
       <c r="Z4" t="n">
         <v>11.34796054612324</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.00748059344522</v>
+        <v>12.00748059344554</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.79923383120146</v>
+        <v>13.79923383120134</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.641703248647566</v>
+        <v>9.641703248647584</v>
       </c>
       <c r="C5" t="n">
-        <v>9.673447597976223</v>
+        <v>9.673447597976407</v>
       </c>
       <c r="D5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="E5" t="n">
-        <v>9.637335262851959</v>
+        <v>9.63733526285219</v>
       </c>
       <c r="F5" t="n">
-        <v>9.642760060478924</v>
+        <v>9.642760060479191</v>
       </c>
       <c r="G5" t="n">
-        <v>9.692628631416524</v>
+        <v>9.692628631416776</v>
       </c>
       <c r="H5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="I5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="J5" t="n">
-        <v>9.699657192540641</v>
+        <v>9.699657192540702</v>
       </c>
       <c r="K5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="L5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="M5" t="n">
-        <v>9.688144498991653</v>
+        <v>9.688144498991916</v>
       </c>
       <c r="N5" t="n">
-        <v>9.651186521682355</v>
+        <v>9.651186521682579</v>
       </c>
       <c r="O5" t="n">
-        <v>9.660171657859641</v>
+        <v>9.660171657859793</v>
       </c>
       <c r="P5" t="n">
-        <v>9.657969183874147</v>
+        <v>9.657969183874229</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.633414064886916</v>
+        <v>9.633414064887267</v>
       </c>
       <c r="R5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="S5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="T5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="U5" t="n">
-        <v>9.663041896209876</v>
+        <v>9.66304189621018</v>
       </c>
       <c r="V5" t="n">
-        <v>9.808249941961199</v>
+        <v>9.808249941961217</v>
       </c>
       <c r="W5" t="n">
-        <v>9.683890780165987</v>
+        <v>9.683890780166299</v>
       </c>
       <c r="X5" t="n">
-        <v>9.63727987620762</v>
+        <v>9.637279876207753</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.725386738747185</v>
+        <v>9.72538673874749</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.640919747574653</v>
+        <v>9.640919747574642</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.683882490790142</v>
+        <v>9.68388249079028</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.744032782492173</v>
+        <v>9.744032782492114</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.808546427168426</v>
+        <v>1.808546427168424</v>
       </c>
       <c r="C6" t="n">
         <v>1.360187039158083</v>
       </c>
       <c r="D6" t="n">
-        <v>2.004159341511054</v>
+        <v>2.004159341511037</v>
       </c>
       <c r="E6" t="n">
-        <v>1.005091550479821</v>
+        <v>1.005091550479823</v>
       </c>
       <c r="F6" t="n">
-        <v>2.291005218752725</v>
+        <v>2.291005218752723</v>
       </c>
       <c r="G6" t="n">
-        <v>2.741822060964088</v>
+        <v>2.741822060964069</v>
       </c>
       <c r="H6" t="n">
-        <v>2.487369125095308</v>
+        <v>2.487369125095309</v>
       </c>
       <c r="I6" t="n">
-        <v>2.27184396265292</v>
+        <v>2.271843962652908</v>
       </c>
       <c r="J6" t="n">
-        <v>2.79647405386766</v>
+        <v>2.796474053867668</v>
       </c>
       <c r="K6" t="n">
-        <v>2.676884611092043</v>
+        <v>2.676884611092053</v>
       </c>
       <c r="L6" t="n">
-        <v>3.118653776122934</v>
+        <v>3.118653776122915</v>
       </c>
       <c r="M6" t="n">
         <v>4.07950198427415</v>
       </c>
       <c r="N6" t="n">
-        <v>2.435939610666559</v>
+        <v>2.435939610666548</v>
       </c>
       <c r="O6" t="n">
-        <v>2.555902970268749</v>
+        <v>2.555902970268737</v>
       </c>
       <c r="P6" t="n">
-        <v>3.53964875427656</v>
+        <v>3.539648754276539</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.418210514482001</v>
+        <v>2.418210514481985</v>
       </c>
       <c r="R6" t="n">
-        <v>2.236183644217955</v>
+        <v>2.236183644217943</v>
       </c>
       <c r="S6" t="n">
-        <v>2.904537062430221</v>
+        <v>2.904537062430207</v>
       </c>
       <c r="T6" t="n">
-        <v>2.687900984593673</v>
+        <v>2.687900984593663</v>
       </c>
       <c r="U6" t="n">
-        <v>3.180717482563802</v>
+        <v>3.180717482563786</v>
       </c>
       <c r="V6" t="n">
-        <v>2.413279684083642</v>
+        <v>2.41327968408363</v>
       </c>
       <c r="W6" t="n">
-        <v>4.144233438266766</v>
+        <v>4.144233438266794</v>
       </c>
       <c r="X6" t="n">
-        <v>3.347200132182197</v>
+        <v>3.347200132182179</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.372699230361687</v>
+        <v>4.372699230361659</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.017517391219517</v>
+        <v>2.017517391219504</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.677037438541516</v>
+        <v>2.677037438541524</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.468790676297749</v>
+        <v>4.468790676297745</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.311260093743859</v>
+        <v>0.3112600937438692</v>
       </c>
       <c r="C7" t="n">
-        <v>0.343004443072508</v>
+        <v>0.3430044430725078</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3068921079482463</v>
+        <v>0.3068921079482462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3123169055752221</v>
+        <v>0.3123169055752219</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3537737410229414</v>
+        <v>0.3537737410229407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3378470473152256</v>
+        <v>0.3378470473152327</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3577013440879496</v>
+        <v>0.3577013440879492</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3207433667786439</v>
+        <v>0.3207433667786154</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3213167674660485</v>
+        <v>0.3213167674660347</v>
       </c>
       <c r="P7" t="n">
-        <v>0.319114293480557</v>
+        <v>0.3191142934805477</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3029709099832016</v>
+        <v>0.3029709099831966</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3241870058162802</v>
+        <v>0.3241870058162724</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3146414702120351</v>
+        <v>0.3146414702120404</v>
       </c>
       <c r="W7" t="n">
-        <v>0.345035889772399</v>
+        <v>0.3450358897724159</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2984249858140301</v>
+        <v>0.2984249858140024</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.394943583843486</v>
+        <v>0.3949435838434835</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3104765926709361</v>
+        <v>0.3104765926709079</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3534393358864307</v>
+        <v>0.3534393358864438</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4135896275884585</v>
+        <v>0.4135896275884582</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="C8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="D8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="E8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="F8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="G8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="H8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="I8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="J8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="K8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="L8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="M8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="O8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="P8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="R8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="S8" t="n">
-        <v>1.172727657520831</v>
+        <v>1.172727657520832</v>
       </c>
       <c r="T8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="U8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="V8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="W8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="X8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.102373783513348</v>
+        <v>1.102373783513346</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.049082753733002</v>
+        <v>5.049082753733011</v>
       </c>
       <c r="C9" t="n">
-        <v>3.757851130353714</v>
+        <v>3.757851130353711</v>
       </c>
       <c r="D9" t="n">
-        <v>5.625852456526849</v>
+        <v>5.625852456526838</v>
       </c>
       <c r="E9" t="n">
-        <v>2.751099573469331</v>
+        <v>2.751099573469335</v>
       </c>
       <c r="F9" t="n">
-        <v>6.487883716644477</v>
+        <v>6.487883716644457</v>
       </c>
       <c r="G9" t="n">
-        <v>7.825672151896196</v>
+        <v>7.825672151896168</v>
       </c>
       <c r="H9" t="n">
-        <v>7.050608915994601</v>
+        <v>7.050608915994604</v>
       </c>
       <c r="I9" t="n">
-        <v>6.415127438177867</v>
+        <v>6.41512743817787</v>
       </c>
       <c r="J9" t="n">
-        <v>8.007987002071324</v>
+        <v>8.007987002071312</v>
       </c>
       <c r="K9" t="n">
-        <v>7.609400194681411</v>
+        <v>7.609400194681413</v>
       </c>
       <c r="L9" t="n">
-        <v>8.911967925828538</v>
+        <v>8.911967925828524</v>
       </c>
       <c r="M9" t="n">
-        <v>11.73248690892268</v>
+        <v>11.73248690892267</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8989676715932</v>
+        <v>6.898967671593208</v>
       </c>
       <c r="O9" t="n">
-        <v>7.277484937138831</v>
+        <v>7.277484937138826</v>
       </c>
       <c r="P9" t="n">
-        <v>10.17808465149645</v>
+        <v>10.17808465149646</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.84669297607253</v>
+        <v>6.846692976072532</v>
       </c>
       <c r="R9" t="n">
-        <v>6.309982073239211</v>
+        <v>6.309982073239214</v>
       </c>
       <c r="S9" t="n">
-        <v>8.280639295330079</v>
+        <v>8.280639295330067</v>
       </c>
       <c r="T9" t="n">
-        <v>7.641882254936751</v>
+        <v>7.641882254936755</v>
       </c>
       <c r="U9" t="n">
-        <v>9.119766576716499</v>
+        <v>9.119766576716488</v>
       </c>
       <c r="V9" t="n">
-        <v>6.911735220799523</v>
+        <v>6.911735220799524</v>
       </c>
       <c r="W9" t="n">
-        <v>11.96071812265863</v>
+        <v>11.96071812265861</v>
       </c>
       <c r="X9" t="n">
         <v>9.610644945680134</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.60955316125101</v>
+        <v>12.60955316125097</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.665239009230431</v>
+        <v>5.665239009230432</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.609850810341969</v>
+        <v>7.609850810341975</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.84543786868385</v>
+        <v>12.84543786868384</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6342955377215306</v>
+        <v>0.6342955377215301</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6924405819959253</v>
+        <v>0.692440581995925</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6536703972002922</v>
+        <v>0.6536703972002921</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7844503369740442</v>
+        <v>0.7844503369740434</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="M10" t="n">
         <v>0.7586621166688439</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6622572118684917</v>
+        <v>0.6622572118684916</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6887501166950948</v>
+        <v>0.6887501166950937</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6822560655722816</v>
+        <v>0.682256065572281</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6098546664727958</v>
+        <v>0.6098546664727957</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6972130882007076</v>
+        <v>0.6972130882007068</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7238465379163483</v>
+        <v>0.7238465379163477</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7586865581061278</v>
+        <v>0.7586865581061271</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6212531104558735</v>
+        <v>0.6212531104558732</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8810384579204197</v>
+        <v>0.8810384579204188</v>
       </c>
       <c r="Z10" t="n">
         <v>0.6319853646816425</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7586621166685086</v>
+        <v>0.7586621166685084</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8885734075950987</v>
+        <v>0.8885734075950981</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="C11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="D11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="E11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="F11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="G11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="H11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="I11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="J11" t="n">
-        <v>8.815069676503533</v>
+        <v>8.815069676503624</v>
       </c>
       <c r="K11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="L11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944517</v>
       </c>
       <c r="M11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="N11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="O11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="P11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="R11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="S11" t="n">
-        <v>8.829648707375455</v>
+        <v>8.829648707375663</v>
       </c>
       <c r="T11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="U11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="V11" t="n">
-        <v>8.928516564887488</v>
+        <v>8.92851656488752</v>
       </c>
       <c r="W11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="X11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.795067988944268</v>
+        <v>8.795067988944497</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.73497582706156</v>
+        <v>10.73497582706161</v>
       </c>
       <c r="C12" t="n">
-        <v>10.10030264342447</v>
+        <v>10.10030264342465</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0184728053493</v>
+        <v>11.01847280534958</v>
       </c>
       <c r="E12" t="n">
-        <v>9.605458647838931</v>
+        <v>9.605458647839173</v>
       </c>
       <c r="F12" t="n">
-        <v>11.44218309430715</v>
+        <v>11.44218309430744</v>
       </c>
       <c r="G12" t="n">
-        <v>12.09974013508967</v>
+        <v>12.09974013508993</v>
       </c>
       <c r="H12" t="n">
-        <v>11.71877684194916</v>
+        <v>11.71877684194942</v>
       </c>
       <c r="I12" t="n">
-        <v>11.40642153298235</v>
+        <v>11.40642153298239</v>
       </c>
       <c r="J12" t="n">
-        <v>12.20935420844393</v>
+        <v>12.20935420844403</v>
       </c>
       <c r="K12" t="n">
-        <v>11.99343696753116</v>
+        <v>11.99343696753145</v>
       </c>
       <c r="L12" t="n">
-        <v>12.63368213645485</v>
+        <v>12.63368213645507</v>
       </c>
       <c r="M12" t="n">
-        <v>14.02003895276667</v>
+        <v>14.02003895276692</v>
       </c>
       <c r="N12" t="n">
-        <v>11.64424131353401</v>
+        <v>11.64424131353431</v>
       </c>
       <c r="O12" t="n">
-        <v>11.83029217662915</v>
+        <v>11.83029217662936</v>
       </c>
       <c r="P12" t="n">
-        <v>13.25601070910306</v>
+        <v>13.25601070910327</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.61854697114878</v>
+        <v>11.618546971149</v>
       </c>
       <c r="R12" t="n">
-        <v>11.35473991188354</v>
+        <v>11.35473991188345</v>
       </c>
       <c r="S12" t="n">
-        <v>12.3233680575671</v>
+        <v>12.32336805756734</v>
       </c>
       <c r="T12" t="n">
-        <v>12.00940272628435</v>
+        <v>12.00940272628457</v>
       </c>
       <c r="U12" t="n">
-        <v>12.73582045844655</v>
+        <v>12.73582045844682</v>
       </c>
       <c r="V12" t="n">
-        <v>11.78396546463773</v>
+        <v>11.78396546463769</v>
       </c>
       <c r="W12" t="n">
-        <v>14.132220399073</v>
+        <v>14.13222039907292</v>
       </c>
       <c r="X12" t="n">
-        <v>12.97709966162575</v>
+        <v>12.97709966162602</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.45113932279097</v>
+        <v>14.45113932279115</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.0378322977473</v>
+        <v>11.03783229774761</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.99365845658913</v>
+        <v>11.99365845658942</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.56708265590566</v>
+        <v>14.56708265590593</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.564995626194605</v>
+        <v>8.564995626194667</v>
       </c>
       <c r="C13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="D13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="E13" t="n">
-        <v>8.593575394296751</v>
+        <v>8.593575394296909</v>
       </c>
       <c r="F13" t="n">
-        <v>8.574518862402009</v>
+        <v>8.574518862402096</v>
       </c>
       <c r="G13" t="n">
-        <v>8.638800529013334</v>
+        <v>8.63880052901353</v>
       </c>
       <c r="H13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="I13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="J13" t="n">
-        <v>8.646126650403605</v>
+        <v>8.646126650403692</v>
       </c>
       <c r="K13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="L13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="M13" t="n">
-        <v>8.626124962844507</v>
+        <v>8.626124962844584</v>
       </c>
       <c r="N13" t="n">
-        <v>8.578739500205542</v>
+        <v>8.578739500205518</v>
       </c>
       <c r="O13" t="n">
-        <v>8.591761436739366</v>
+        <v>8.591761436739365</v>
       </c>
       <c r="P13" t="n">
-        <v>8.588569445445012</v>
+        <v>8.588569445445202</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.552982316355038</v>
+        <v>8.55298231635523</v>
       </c>
       <c r="R13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="S13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="T13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="U13" t="n">
-        <v>8.595921202478712</v>
+        <v>8.59592120247885</v>
       </c>
       <c r="V13" t="n">
         <v>8.742460796343311</v>
       </c>
       <c r="W13" t="n">
-        <v>8.626136976432567</v>
+        <v>8.626136976432669</v>
       </c>
       <c r="X13" t="n">
-        <v>8.55858494147687</v>
+        <v>8.558584941476946</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.68627604704791</v>
+        <v>8.686276047048079</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.563860117389346</v>
+        <v>8.56386011738943</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.626124962844338</v>
+        <v>8.626124962844422</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.689979666454372</v>
+        <v>8.689979666454706</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="C14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="D14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="E14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="F14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7648425727118431</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="H14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="I14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7651058674433622</v>
+        <v>0.7651058674433601</v>
       </c>
       <c r="K14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="L14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605688</v>
       </c>
       <c r="M14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="N14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7648425727118431</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7648425727118431</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="R14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="S14" t="n">
         <v>0.8066563119917636</v>
       </c>
       <c r="T14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7648425727118433</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7652227846182835</v>
+        <v>0.7652227846182831</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7648425727118431</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7648425727118431</v>
+        <v>0.7648425727118424</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.772075593560569</v>
+        <v>0.7720755935605687</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.711983431677866</v>
+        <v>2.71198343167787</v>
       </c>
       <c r="C15" t="n">
-        <v>2.077310248040765</v>
+        <v>2.077310248040764</v>
       </c>
       <c r="D15" t="n">
-        <v>2.995480409965599</v>
+        <v>2.995480409965594</v>
       </c>
       <c r="E15" t="n">
         <v>1.582466252455222</v>
       </c>
       <c r="F15" t="n">
-        <v>3.419190698923446</v>
+        <v>3.419190698923441</v>
       </c>
       <c r="G15" t="n">
-        <v>4.069514718857243</v>
+        <v>4.06951471885723</v>
       </c>
       <c r="H15" t="n">
         <v>3.695784446565467</v>
       </c>
       <c r="I15" t="n">
-        <v>3.383429137598652</v>
+        <v>3.383429137598657</v>
       </c>
       <c r="J15" t="n">
-        <v>4.159390399383764</v>
+        <v>4.15939039938376</v>
       </c>
       <c r="K15" t="n">
-        <v>3.970444572147462</v>
+        <v>3.970444572147469</v>
       </c>
       <c r="L15" t="n">
-        <v>4.610689741071166</v>
+        <v>4.610689741071158</v>
       </c>
       <c r="M15" t="n">
-        <v>5.997046557382972</v>
+        <v>5.997046557382963</v>
       </c>
       <c r="N15" t="n">
-        <v>3.621248918150316</v>
+        <v>3.621248918150318</v>
       </c>
       <c r="O15" t="n">
-        <v>3.80006676039673</v>
+        <v>3.800066760396727</v>
       </c>
       <c r="P15" t="n">
-        <v>5.225785292870626</v>
+        <v>5.225785292870619</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.595554575765072</v>
+        <v>3.595554575765068</v>
       </c>
       <c r="R15" t="n">
-        <v>3.331747516499832</v>
+        <v>3.331747516499838</v>
       </c>
       <c r="S15" t="n">
-        <v>4.300375662183394</v>
+        <v>4.300375662183392</v>
       </c>
       <c r="T15" t="n">
         <v>3.986410330900647</v>
       </c>
       <c r="U15" t="n">
-        <v>4.705595042214121</v>
+        <v>4.705595042214116</v>
       </c>
       <c r="V15" t="n">
         <v>3.620671684368443</v>
       </c>
       <c r="W15" t="n">
-        <v>6.101994982840576</v>
+        <v>6.101994982840556</v>
       </c>
       <c r="X15" t="n">
-        <v>4.946874245393322</v>
+        <v>4.946874245393324</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.42814692740726</v>
+        <v>6.428146927407242</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.0148399023636</v>
+        <v>3.014839902363599</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.970666061205435</v>
+        <v>3.970666061205436</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.544090260521958</v>
+        <v>6.544090260521959</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5420032308109027</v>
+        <v>0.5420032308109031</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5705829989130581</v>
+        <v>0.5705829989130582</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5515264670183045</v>
+        <v>0.5515264670183043</v>
       </c>
       <c r="G16" t="n">
         <v>0.6085751127809088</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5961628413434277</v>
+        <v>0.5961628413434273</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6031325674608004</v>
+        <v>0.6031325674608</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5557471048218495</v>
+        <v>0.5557471048218494</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5615360205069342</v>
+        <v>0.561536020506934</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5583440292125832</v>
+        <v>0.5583440292125829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5299899209713386</v>
+        <v>0.5299899209713387</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="U16" t="n">
         <v>0.5656957862462834</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5791670160740678</v>
+        <v>0.5791670160740674</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5959115602001342</v>
+        <v>0.595911560200134</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5283595252444447</v>
+        <v>0.5283595252444451</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.663283651664214</v>
+        <v>0.6632836516642132</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.5408677220056423</v>
+        <v>0.5408677220056418</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6031325674606353</v>
+        <v>0.603132567460635</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.666987271070667</v>
+        <v>0.6669872710706661</v>
       </c>
     </row>
   </sheetData>
@@ -9466,7 +9466,7 @@
         <v>1.912244813698284</v>
       </c>
       <c r="J2" t="n">
-        <v>3.730732011124479</v>
+        <v>3.73073201112448</v>
       </c>
       <c r="K2" t="n">
         <v>1.601847606845427</v>
@@ -9487,7 +9487,7 @@
         <v>8.51700375779572</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.999607353231886</v>
+        <v>1.999607353231887</v>
       </c>
       <c r="R2" t="n">
         <v>1.166937416725593</v>
@@ -9505,7 +9505,7 @@
         <v>4.298204240803964</v>
       </c>
       <c r="W2" t="n">
-        <v>8.871165676564654</v>
+        <v>8.871165676564653</v>
       </c>
       <c r="X2" t="n">
         <v>6.926897138375804</v>
@@ -9575,7 +9575,7 @@
         <v>0.3522881000333126</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3005534599159111</v>
+        <v>0.300553459915911</v>
       </c>
       <c r="R3" t="n">
         <v>0.4068842764428005</v>
@@ -9678,7 +9678,7 @@
         <v>10.63863335325507</v>
       </c>
       <c r="V4" t="n">
-        <v>10.98585945185223</v>
+        <v>10.98585945185224</v>
       </c>
       <c r="W4" t="n">
         <v>12.40868756558767</v>
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3185438260392491</v>
+        <v>0.3185438260392492</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5339331938830645</v>
+        <v>0.5339331938830646</v>
       </c>
       <c r="D6" t="n">
         <v>0.4488332661218355</v>
@@ -9830,7 +9830,7 @@
         <v>1.123499883143904</v>
       </c>
       <c r="N6" t="n">
-        <v>2.147925049542142</v>
+        <v>2.147925049542143</v>
       </c>
       <c r="O6" t="n">
         <v>2.502583783488368</v>
@@ -9860,7 +9860,7 @@
         <v>3.346655975215767</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63799292379978</v>
+        <v>2.637992923799781</v>
       </c>
       <c r="Y6" t="n">
         <v>3.411673014026093</v>
@@ -10112,13 +10112,13 @@
         <v>2.999734487559296</v>
       </c>
       <c r="T9" t="n">
-        <v>3.964249481152868</v>
+        <v>3.964249481152869</v>
       </c>
       <c r="U9" t="n">
         <v>4.508205445052051</v>
       </c>
       <c r="V9" t="n">
-        <v>4.82162604667529</v>
+        <v>4.821626046675291</v>
       </c>
       <c r="W9" t="n">
         <v>9.727255758815058</v>
@@ -10136,7 +10136,7 @@
         <v>6.030424771655515</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.049159828013897</v>
+        <v>6.049159828013895</v>
       </c>
     </row>
     <row r="10">

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide resource use fossils results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide resource use fossils results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.447833245640399</v>
+        <v>7.447833245640384</v>
       </c>
       <c r="C2" t="n">
         <v>2.492213682489139</v>
       </c>
       <c r="D2" t="n">
-        <v>5.164122086317957</v>
+        <v>5.164122086317938</v>
       </c>
       <c r="E2" t="n">
-        <v>4.927132712247905</v>
+        <v>4.9271327122479</v>
       </c>
       <c r="F2" t="n">
-        <v>5.279227486555151</v>
+        <v>5.279227486555144</v>
       </c>
       <c r="G2" t="n">
-        <v>8.615699714325332</v>
+        <v>8.6156997143253</v>
       </c>
       <c r="H2" t="n">
-        <v>8.753968399869343</v>
+        <v>8.753968399869313</v>
       </c>
       <c r="I2" t="n">
-        <v>4.506426911148541</v>
+        <v>4.506426911148564</v>
       </c>
       <c r="J2" t="n">
-        <v>8.965957757589077</v>
+        <v>8.965957757589074</v>
       </c>
       <c r="K2" t="n">
-        <v>8.064241988351959</v>
+        <v>8.064241988351926</v>
       </c>
       <c r="L2" t="n">
-        <v>10.50356329588289</v>
+        <v>10.50356329588285</v>
       </c>
       <c r="M2" t="n">
-        <v>14.3785728390972</v>
+        <v>14.37857283909718</v>
       </c>
       <c r="N2" t="n">
-        <v>9.632334195226992</v>
+        <v>9.632334195226957</v>
       </c>
       <c r="O2" t="n">
-        <v>8.168281704976986</v>
+        <v>8.168281704976959</v>
       </c>
       <c r="P2" t="n">
-        <v>10.71483095545989</v>
+        <v>10.71483095545987</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.219320480035445</v>
+        <v>7.219320480035434</v>
       </c>
       <c r="R2" t="n">
-        <v>5.668648276080013</v>
+        <v>5.668648276079995</v>
       </c>
       <c r="S2" t="n">
-        <v>8.356560212666444</v>
+        <v>8.356560212666427</v>
       </c>
       <c r="T2" t="n">
-        <v>8.111127332183004</v>
+        <v>8.111127332182983</v>
       </c>
       <c r="U2" t="n">
-        <v>12.18045462212797</v>
+        <v>12.18045462212796</v>
       </c>
       <c r="V2" t="n">
-        <v>7.695786029742363</v>
+        <v>7.69578602974235</v>
       </c>
       <c r="W2" t="n">
-        <v>12.33379605150573</v>
+        <v>12.33379605150572</v>
       </c>
       <c r="X2" t="n">
-        <v>6.873000801496119</v>
+        <v>6.873000801496092</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.21010052673727</v>
+        <v>13.21010052673725</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.964520486667816</v>
+        <v>8.964520486667801</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.658881781521505</v>
+        <v>7.658881781521472</v>
       </c>
       <c r="AB2" t="n">
         <v>14.31960307595338</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5126911469016983</v>
+        <v>0.5126911469017287</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6325378605451548</v>
+        <v>0.632537860545154</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5479928287847972</v>
+        <v>0.5479928287847964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5159438943713717</v>
+        <v>0.515943894371371</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6841446542711196</v>
+        <v>0.6841446542710927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6431263436970783</v>
+        <v>0.6431263436970518</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6579527537738278</v>
+        <v>0.657952753773827</v>
       </c>
       <c r="N3" t="n">
-        <v>0.544619044827197</v>
+        <v>0.5446190448271937</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5748698358368942</v>
+        <v>0.5748698358368005</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5674546360101913</v>
+        <v>0.5674546360101528</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4847834601767854</v>
+        <v>0.4847834601767609</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5854410390484456</v>
+        <v>0.5854410390484962</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5872812088878817</v>
+        <v>0.5872812088878813</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6547264120603784</v>
+        <v>0.6547264120603469</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4977987164786613</v>
+        <v>0.4977987164786781</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7959863018273532</v>
+        <v>0.7959863018273545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5100532873595097</v>
+        <v>0.5100532873595056</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6546985037512867</v>
+        <v>0.6546985037512472</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8166178225224952</v>
+        <v>0.8166178225224943</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.4397886679334</v>
+        <v>12.43978866793333</v>
       </c>
       <c r="C4" t="n">
-        <v>10.61944018000675</v>
+        <v>10.61944018000669</v>
       </c>
       <c r="D4" t="n">
-        <v>11.60740276705072</v>
+        <v>11.60740276705064</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5012642615204</v>
+        <v>11.50126426152034</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6373650117619</v>
+        <v>11.63736501176185</v>
       </c>
       <c r="G4" t="n">
-        <v>12.86546228198861</v>
+        <v>12.86546228198853</v>
       </c>
       <c r="H4" t="n">
-        <v>12.91585959423652</v>
+        <v>12.91585959423645</v>
       </c>
       <c r="I4" t="n">
-        <v>11.36768059874815</v>
+        <v>11.36768059874807</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00482248972517</v>
+        <v>13.00482248972513</v>
       </c>
       <c r="K4" t="n">
-        <v>12.66446241641487</v>
+        <v>12.66446241641479</v>
       </c>
       <c r="L4" t="n">
-        <v>13.55356638905293</v>
+        <v>13.55356638905286</v>
       </c>
       <c r="M4" t="n">
-        <v>14.96802997899778</v>
+        <v>14.96802997899771</v>
       </c>
       <c r="N4" t="n">
         <v>13.23601361235247</v>
       </c>
       <c r="O4" t="n">
-        <v>12.70238367142865</v>
+        <v>12.70238367142858</v>
       </c>
       <c r="P4" t="n">
-        <v>13.63057097013863</v>
+        <v>13.63057097013856</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.35649844820276</v>
+        <v>12.3564984482027</v>
       </c>
       <c r="R4" t="n">
-        <v>11.79129663877336</v>
+        <v>11.7912966387733</v>
       </c>
       <c r="S4" t="n">
-        <v>12.77100897660359</v>
+        <v>12.77100897660353</v>
       </c>
       <c r="T4" t="n">
-        <v>12.68155157368578</v>
+        <v>12.68155157368571</v>
       </c>
       <c r="U4" t="n">
-        <v>14.16477358641716</v>
+        <v>14.1647735864171</v>
       </c>
       <c r="V4" t="n">
         <v>12.63904258582776</v>
       </c>
       <c r="W4" t="n">
-        <v>14.22066473679936</v>
+        <v>14.2206647367993</v>
       </c>
       <c r="X4" t="n">
-        <v>12.23026899206616</v>
+        <v>12.23026899206607</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5400674279346</v>
+        <v>14.54006742793446</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.99260335744713</v>
+        <v>12.99260335744704</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.51671338100504</v>
+        <v>12.51671338100496</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.95309881131322</v>
+        <v>14.95309881131316</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.912010809493236</v>
+        <v>9.912010809493159</v>
       </c>
       <c r="C5" t="n">
-        <v>9.94161018032419</v>
+        <v>9.941610180324142</v>
       </c>
       <c r="D5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="E5" t="n">
-        <v>9.905119196454811</v>
+        <v>9.905119196454748</v>
       </c>
       <c r="F5" t="n">
-        <v>9.901204075710801</v>
+        <v>9.901204075710757</v>
       </c>
       <c r="G5" t="n">
-        <v>9.974503599620652</v>
+        <v>9.974503599620558</v>
       </c>
       <c r="H5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="I5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="J5" t="n">
-        <v>9.971248170982255</v>
+        <v>9.971248170982262</v>
       </c>
       <c r="K5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="L5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="M5" t="n">
-        <v>9.96702507355284</v>
+        <v>9.967025073552778</v>
       </c>
       <c r="N5" t="n">
-        <v>9.923648153370767</v>
+        <v>9.923648153370669</v>
       </c>
       <c r="O5" t="n">
-        <v>9.934674211471078</v>
+        <v>9.934674211470975</v>
       </c>
       <c r="P5" t="n">
-        <v>9.931971458207917</v>
+        <v>9.931971458207819</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.901838785390595</v>
+        <v>9.901838785390581</v>
       </c>
       <c r="R5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="S5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="T5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="U5" t="n">
-        <v>9.93852729090835</v>
+        <v>9.938527290908278</v>
       </c>
       <c r="V5" t="n">
         <v>10.04807605090424</v>
       </c>
       <c r="W5" t="n">
-        <v>9.963780995781278</v>
+        <v>9.963780995781214</v>
       </c>
       <c r="X5" t="n">
-        <v>9.906582693479779</v>
+        <v>9.906582693479667</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.01526856684397</v>
+        <v>10.01526856684389</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.911049340665416</v>
+        <v>9.911049340665356</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.963770823530322</v>
+        <v>9.9637708235303</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.03141924649586</v>
+        <v>10.03141924649581</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.908329442078256</v>
+        <v>2.908329442078246</v>
       </c>
       <c r="C6" t="n">
-        <v>1.087980954151604</v>
+        <v>1.087980954151605</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075943541195578</v>
+        <v>2.075943541195562</v>
       </c>
       <c r="E6" t="n">
         <v>1.969805035665247</v>
       </c>
       <c r="F6" t="n">
-        <v>2.105905785906747</v>
+        <v>2.105905785906746</v>
       </c>
       <c r="G6" t="n">
-        <v>3.324107703797065</v>
+        <v>3.324107703797045</v>
       </c>
       <c r="H6" t="n">
-        <v>3.384400368381375</v>
+        <v>3.384400368381354</v>
       </c>
       <c r="I6" t="n">
-        <v>1.836221372892992</v>
+        <v>1.836221372892975</v>
       </c>
       <c r="J6" t="n">
-        <v>3.444788821620667</v>
+        <v>3.444788821620651</v>
       </c>
       <c r="K6" t="n">
-        <v>3.133003190559717</v>
+        <v>3.1330031905597</v>
       </c>
       <c r="L6" t="n">
-        <v>4.022107163197775</v>
+        <v>4.02210716319776</v>
       </c>
       <c r="M6" t="n">
-        <v>5.43657075314263</v>
+        <v>5.436570753142629</v>
       </c>
       <c r="N6" t="n">
-        <v>3.704554386497319</v>
+        <v>3.704554386497382</v>
       </c>
       <c r="O6" t="n">
-        <v>3.161029093237113</v>
+        <v>3.161029093237099</v>
       </c>
       <c r="P6" t="n">
-        <v>4.089216391947095</v>
+        <v>4.08921639194708</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.825039222347621</v>
+        <v>2.825039222347607</v>
       </c>
       <c r="R6" t="n">
-        <v>2.259837412918214</v>
+        <v>2.259837412918197</v>
       </c>
       <c r="S6" t="n">
-        <v>3.239549750748453</v>
+        <v>3.239549750748441</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15009234783063</v>
+        <v>3.150092347830619</v>
       </c>
       <c r="U6" t="n">
-        <v>4.623419008225602</v>
+        <v>4.623419008225595</v>
       </c>
       <c r="V6" t="n">
-        <v>2.971139046777451</v>
+        <v>2.971139046777445</v>
       </c>
       <c r="W6" t="n">
-        <v>4.679310158607829</v>
+        <v>4.679310158607819</v>
       </c>
       <c r="X6" t="n">
-        <v>2.688914413874627</v>
+        <v>2.688914413874588</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.008608202079447</v>
+        <v>5.008608202079378</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.461144131591986</v>
+        <v>3.461144131591974</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.98525415514989</v>
+        <v>2.985254155149876</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.421639585458077</v>
+        <v>5.421639585458079</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3805515836380799</v>
+        <v>0.3805515836380672</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4101509544690488</v>
+        <v>0.4101509544690481</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3736599705996661</v>
+        <v>0.3736599705996656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3697448498556529</v>
+        <v>0.3697448498556521</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4331490214291091</v>
+        <v>0.4331490214290904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="J7" t="n">
-        <v>0.411214502877755</v>
+        <v>0.4112145028777664</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4355658476976917</v>
+        <v>0.4355658476976909</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3921889275156182</v>
+        <v>0.3921889275155727</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3933196332795364</v>
+        <v>0.3933196332794928</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3906168800163756</v>
+        <v>0.3906168800163354</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3703795595354522</v>
+        <v>0.3703795595354819</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3971727127168114</v>
+        <v>0.3971727127167971</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3801725118539339</v>
+        <v>0.3801725118539333</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4224264175897347</v>
+        <v>0.4224264175897295</v>
       </c>
       <c r="X7" t="n">
-        <v>0.365228115288236</v>
+        <v>0.3652281152881794</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.483809340988818</v>
+        <v>0.4838093409887878</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3795901148102632</v>
+        <v>0.3795901148102595</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4323115976751807</v>
+        <v>0.4323115976751964</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.499960020640713</v>
+        <v>0.4999600206407124</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4527186931137128</v>
+        <v>0.4527186931136037</v>
       </c>
       <c r="C2" t="n">
-        <v>1.239386790592513</v>
+        <v>1.239386790592515</v>
       </c>
       <c r="D2" t="n">
-        <v>1.898875477566867</v>
+        <v>1.89887547756675</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9752047896899272</v>
+        <v>0.9752047896899265</v>
       </c>
       <c r="F2" t="n">
-        <v>3.248656133415323</v>
+        <v>3.248656133415325</v>
       </c>
       <c r="G2" t="n">
-        <v>4.07489890504467</v>
+        <v>4.074898905044572</v>
       </c>
       <c r="H2" t="n">
-        <v>3.936192235231978</v>
+        <v>3.936192235231875</v>
       </c>
       <c r="I2" t="n">
-        <v>1.865018110449991</v>
+        <v>1.865018110449885</v>
       </c>
       <c r="J2" t="n">
-        <v>3.659213705010329</v>
+        <v>3.659213705010268</v>
       </c>
       <c r="K2" t="n">
-        <v>4.775695340925179</v>
+        <v>4.775695340925068</v>
       </c>
       <c r="L2" t="n">
-        <v>3.067817171627304</v>
+        <v>3.067817171627085</v>
       </c>
       <c r="M2" t="n">
-        <v>3.180716984534017</v>
+        <v>3.180716984534005</v>
       </c>
       <c r="N2" t="n">
-        <v>4.946517093373774</v>
+        <v>4.946517093373798</v>
       </c>
       <c r="O2" t="n">
-        <v>5.243654751552659</v>
+        <v>5.24365475155252</v>
       </c>
       <c r="P2" t="n">
-        <v>7.750445416177325</v>
+        <v>7.750445416177286</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.827897105233619</v>
+        <v>1.827897105233515</v>
       </c>
       <c r="R2" t="n">
-        <v>1.605140195626585</v>
+        <v>1.605140195626491</v>
       </c>
       <c r="S2" t="n">
-        <v>4.279609171758623</v>
+        <v>4.279609171758525</v>
       </c>
       <c r="T2" t="n">
-        <v>4.217238357631144</v>
+        <v>4.217238357631098</v>
       </c>
       <c r="U2" t="n">
-        <v>4.652826929387238</v>
+        <v>4.652826929387126</v>
       </c>
       <c r="V2" t="n">
         <v>2.532059221991487</v>
       </c>
       <c r="W2" t="n">
-        <v>7.756992823094524</v>
+        <v>7.756992823094373</v>
       </c>
       <c r="X2" t="n">
-        <v>7.757174264095962</v>
+        <v>7.757174264095851</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.857804561769147</v>
+        <v>6.857804561769028</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.045207274723909</v>
+        <v>2.045207274723718</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.222507291209996</v>
+        <v>6.222507291209786</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.303180228683957</v>
+        <v>3.303180228683955</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3159960696864302</v>
+        <v>0.315996069686256</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4013084754063462</v>
+        <v>0.4013084754063456</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="E3" t="n">
-        <v>0.344820260546899</v>
+        <v>0.3448202605468988</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3286588426999116</v>
+        <v>0.3286588426999109</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4239233395658135</v>
+        <v>0.4239233395657643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4006215163319038</v>
+        <v>0.4006215163317853</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4013369365631919</v>
+        <v>0.4013369365631806</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3360941762167959</v>
+        <v>0.3360941762166506</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3551365704822576</v>
+        <v>0.3551365704821421</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3504688195260565</v>
+        <v>0.3504688195258236</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2984286224922353</v>
+        <v>0.2984286224920734</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3611611111837753</v>
+        <v>0.3611611111836594</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3689785641755745</v>
+        <v>0.3689785641755737</v>
       </c>
       <c r="W3" t="n">
-        <v>0.405405021598257</v>
+        <v>0.4054050215980893</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3066215203872328</v>
+        <v>0.3066215203869585</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.493248372157898</v>
+        <v>0.4932483721578211</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3143355788448321</v>
+        <v>0.314335578844645</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4053874537576654</v>
+        <v>0.4053874537576069</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4985697769057375</v>
+        <v>0.4985697769057367</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.346870153489821</v>
+        <v>9.346870153489721</v>
       </c>
       <c r="C4" t="n">
-        <v>9.631009198857511</v>
+        <v>9.631009198857583</v>
       </c>
       <c r="D4" t="n">
-        <v>9.873977319792665</v>
+        <v>9.873977319792527</v>
       </c>
       <c r="E4" t="n">
-        <v>9.529068300609328</v>
+        <v>9.529068300609374</v>
       </c>
       <c r="F4" t="n">
-        <v>10.36515363889167</v>
+        <v>10.36515363889171</v>
       </c>
       <c r="G4" t="n">
-        <v>10.66711230695118</v>
+        <v>10.66711230695102</v>
       </c>
       <c r="H4" t="n">
-        <v>10.6165553545804</v>
+        <v>10.61655535458029</v>
       </c>
       <c r="I4" t="n">
-        <v>9.861636707051844</v>
+        <v>9.861636707051742</v>
       </c>
       <c r="J4" t="n">
         <v>10.52973858962251</v>
       </c>
       <c r="K4" t="n">
-        <v>10.92254437866239</v>
+        <v>10.92254437866229</v>
       </c>
       <c r="L4" t="n">
-        <v>10.30004284087126</v>
+        <v>10.30004284087115</v>
       </c>
       <c r="M4" t="n">
-        <v>10.33861934569844</v>
+        <v>10.33861934569843</v>
       </c>
       <c r="N4" t="n">
-        <v>10.98480690153959</v>
+        <v>10.98480690153955</v>
       </c>
       <c r="O4" t="n">
-        <v>11.09311008877926</v>
+        <v>11.09311008877916</v>
       </c>
       <c r="P4" t="n">
-        <v>12.00680584981278</v>
+        <v>12.00680584981273</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.848106536547322</v>
+        <v>9.848106536547228</v>
       </c>
       <c r="R4" t="n">
-        <v>9.766914258739259</v>
+        <v>9.766914258739138</v>
       </c>
       <c r="S4" t="n">
-        <v>10.74172679533908</v>
+        <v>10.74172679533898</v>
       </c>
       <c r="T4" t="n">
-        <v>10.71899336598472</v>
+        <v>10.71899336598461</v>
       </c>
       <c r="U4" t="n">
-        <v>10.87776028545054</v>
+        <v>10.87776028545043</v>
       </c>
       <c r="V4" t="n">
-        <v>10.2121095516063</v>
+        <v>10.21210955160631</v>
       </c>
       <c r="W4" t="n">
-        <v>12.00919230275064</v>
+        <v>12.00919230275047</v>
       </c>
       <c r="X4" t="n">
-        <v>12.00925843586502</v>
+        <v>12.00925843586493</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.68144874029913</v>
+        <v>11.68144874029904</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.92731354154167</v>
+        <v>9.927313541541558</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.44989034521752</v>
+        <v>11.44989034521739</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.38570633475113</v>
+        <v>10.38570633475115</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.297036362728635</v>
+        <v>9.297036362728555</v>
       </c>
       <c r="C5" t="n">
-        <v>9.325539494184644</v>
+        <v>9.32553949418466</v>
       </c>
       <c r="D5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="E5" t="n">
-        <v>9.299300542085627</v>
+        <v>9.299300542085607</v>
       </c>
       <c r="F5" t="n">
-        <v>9.30084891476522</v>
+        <v>9.300848914765275</v>
       </c>
       <c r="G5" t="n">
-        <v>9.336374585253724</v>
+        <v>9.336374585253649</v>
       </c>
       <c r="H5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="I5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="J5" t="n">
         <v>9.342020001170557</v>
       </c>
       <c r="K5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="L5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="M5" t="n">
-        <v>9.3255679553414</v>
+        <v>9.325567955341374</v>
       </c>
       <c r="N5" t="n">
-        <v>9.304361886555084</v>
+        <v>9.304361886554997</v>
       </c>
       <c r="O5" t="n">
-        <v>9.311302615657944</v>
+        <v>9.311302615657679</v>
       </c>
       <c r="P5" t="n">
-        <v>9.309601275245837</v>
+        <v>9.309601275245608</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.290633234513708</v>
+        <v>9.290633234513656</v>
       </c>
       <c r="R5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="S5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="T5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="U5" t="n">
-        <v>9.313498489999672</v>
+        <v>9.313498489999654</v>
       </c>
       <c r="V5" t="n">
-        <v>9.423692052007889</v>
+        <v>9.423692052007887</v>
       </c>
       <c r="W5" t="n">
-        <v>9.329624875807559</v>
+        <v>9.329624875807488</v>
       </c>
       <c r="X5" t="n">
-        <v>9.29361944959064</v>
+        <v>9.293619449590457</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.361642745578044</v>
+        <v>9.36164274557782</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.296431133315279</v>
+        <v>9.296431133315247</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.329618472535932</v>
+        <v>9.329618472535927</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.363458758476611</v>
+        <v>9.363458758476645</v>
       </c>
     </row>
     <row r="6">
@@ -1622,82 +1622,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2839149782667082</v>
+        <v>0.2839149782665836</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5680540236344848</v>
+        <v>0.5680540236344849</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8110221445695507</v>
+        <v>0.8110221445694556</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4661131253862701</v>
+        <v>0.4661131253862703</v>
       </c>
       <c r="F6" t="n">
-        <v>1.302198463668609</v>
+        <v>1.302198463668608</v>
       </c>
       <c r="G6" t="n">
-        <v>1.59666328203977</v>
+        <v>1.596663282039632</v>
       </c>
       <c r="H6" t="n">
-        <v>1.553600179357279</v>
+        <v>1.553600179357156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7986815318287321</v>
+        <v>0.7986815318286061</v>
       </c>
       <c r="J6" t="n">
-        <v>1.44239262709063</v>
+        <v>1.442392627090601</v>
       </c>
       <c r="K6" t="n">
-        <v>1.859589203439274</v>
+        <v>1.859589203439153</v>
       </c>
       <c r="L6" t="n">
-        <v>1.237087665648174</v>
+        <v>1.237087665648107</v>
       </c>
       <c r="M6" t="n">
-        <v>1.275664170475352</v>
+        <v>1.275664170475308</v>
       </c>
       <c r="N6" t="n">
-        <v>1.921851726316535</v>
+        <v>1.921851726316424</v>
       </c>
       <c r="O6" t="n">
-        <v>2.022661063867877</v>
+        <v>2.022661063867781</v>
       </c>
       <c r="P6" t="n">
-        <v>2.936356824901386</v>
+        <v>2.936356824901349</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7851513613242134</v>
+        <v>0.7851513613240905</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7039590835161424</v>
+        <v>0.7039590835160106</v>
       </c>
       <c r="S6" t="n">
-        <v>1.678771620115997</v>
+        <v>1.678771620115854</v>
       </c>
       <c r="T6" t="n">
-        <v>1.656038190761629</v>
+        <v>1.656038190761482</v>
       </c>
       <c r="U6" t="n">
-        <v>1.807311260539146</v>
+        <v>1.807311260539052</v>
       </c>
       <c r="V6" t="n">
-        <v>1.027510630486075</v>
+        <v>1.027510630486076</v>
       </c>
       <c r="W6" t="n">
-        <v>2.938743277839238</v>
+        <v>2.938743277839086</v>
       </c>
       <c r="X6" t="n">
-        <v>2.938809410953632</v>
+        <v>2.938809410953541</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.618493565076034</v>
+        <v>2.618493565075926</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8643583663185437</v>
+        <v>0.8643583663184249</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.386935169994395</v>
+        <v>2.386935169994322</v>
       </c>
       <c r="AB6" t="n">
         <v>1.322751159528058</v>
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.234081187505522</v>
+        <v>0.2340811875054089</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2625843189615653</v>
+        <v>0.262584318961565</v>
       </c>
       <c r="D7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2363453668625069</v>
+        <v>0.2363453668625064</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2378937395421729</v>
+        <v>0.2378937395421721</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2659255603423566</v>
+        <v>0.265925560342258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="I7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.25467403863878</v>
+        <v>0.2546740386386498</v>
       </c>
       <c r="K7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="L7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2626127801182881</v>
+        <v>0.2626127801182438</v>
       </c>
       <c r="N7" t="n">
-        <v>0.241406711332021</v>
+        <v>0.2414067113318615</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2408535907465451</v>
+        <v>0.2408535907462993</v>
       </c>
       <c r="P7" t="n">
-        <v>0.239152250334439</v>
+        <v>0.2391522503342227</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2276780592906287</v>
+        <v>0.2276780592905153</v>
       </c>
       <c r="R7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="S7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="T7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="U7" t="n">
-        <v>0.243049465088285</v>
+        <v>0.2430494650882752</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2390931308876604</v>
+        <v>0.2390931308876599</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2591758508961917</v>
+        <v>0.2591758508961092</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2231704246792883</v>
+        <v>0.2231704246790871</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.298687570354957</v>
+        <v>0.2986875703546742</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2334759580922207</v>
+        <v>0.233475958092118</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.266663297312849</v>
+        <v>0.2666632973127955</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3005035832535593</v>
+        <v>0.3005035832535589</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.998970135063044</v>
+        <v>5.998970135063172</v>
       </c>
       <c r="C2" t="n">
-        <v>2.271660145245376</v>
+        <v>2.27166014524541</v>
       </c>
       <c r="D2" t="n">
-        <v>5.685242923917466</v>
+        <v>5.685242923917497</v>
       </c>
       <c r="E2" t="n">
-        <v>4.777098236304328</v>
+        <v>4.777098236304358</v>
       </c>
       <c r="F2" t="n">
-        <v>4.453241345966707</v>
+        <v>4.453241345966718</v>
       </c>
       <c r="G2" t="n">
-        <v>8.137326732081883</v>
+        <v>8.137326732081869</v>
       </c>
       <c r="H2" t="n">
-        <v>7.538247256711459</v>
+        <v>7.538247256711482</v>
       </c>
       <c r="I2" t="n">
-        <v>4.26058045466707</v>
+        <v>4.260580454667095</v>
       </c>
       <c r="J2" t="n">
-        <v>8.411129865175203</v>
+        <v>8.411129865175164</v>
       </c>
       <c r="K2" t="n">
-        <v>6.758887130398315</v>
+        <v>6.758887130398337</v>
       </c>
       <c r="L2" t="n">
-        <v>9.191289528273103</v>
+        <v>9.191289528273424</v>
       </c>
       <c r="M2" t="n">
-        <v>13.06751503116306</v>
+        <v>13.06751503116309</v>
       </c>
       <c r="N2" t="n">
-        <v>8.828691425951508</v>
+        <v>8.828691425951524</v>
       </c>
       <c r="O2" t="n">
-        <v>8.401223428232804</v>
+        <v>8.401223428232839</v>
       </c>
       <c r="P2" t="n">
-        <v>10.84173333164018</v>
+        <v>10.84173333164021</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.527130490302937</v>
+        <v>6.527130490302932</v>
       </c>
       <c r="R2" t="n">
-        <v>6.106761152048571</v>
+        <v>6.106761152048601</v>
       </c>
       <c r="S2" t="n">
-        <v>7.659557008012544</v>
+        <v>7.659557008012582</v>
       </c>
       <c r="T2" t="n">
-        <v>6.643698872762307</v>
+        <v>6.643698872762322</v>
       </c>
       <c r="U2" t="n">
-        <v>10.72475147658789</v>
+        <v>10.72475147658791</v>
       </c>
       <c r="V2" t="n">
-        <v>7.011658200510054</v>
+        <v>7.011658200510038</v>
       </c>
       <c r="W2" t="n">
-        <v>12.64196944521854</v>
+        <v>12.64196944521855</v>
       </c>
       <c r="X2" t="n">
-        <v>7.19268591950693</v>
+        <v>7.192685919506868</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.0213268506007</v>
+        <v>13.02132685060074</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.865664115637982</v>
+        <v>7.865664115637992</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.519168549220486</v>
+        <v>6.519168549220528</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.87671240939943</v>
+        <v>13.87671240939963</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4826402455625103</v>
+        <v>0.4826402455624939</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5967696972033498</v>
+        <v>0.5967696972033221</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5174966744998848</v>
+        <v>0.5174966744998862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4853833770912805</v>
+        <v>0.4853833770912822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6440436221681483</v>
+        <v>0.6440436221681477</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6058679781338401</v>
+        <v>0.605867978133853</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6194804031251355</v>
+        <v>0.619480403125138</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5126966183496072</v>
+        <v>0.5126966183496219</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5411741915945462</v>
+        <v>0.5411741915944913</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5341936502880762</v>
+        <v>0.5341936502880915</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.456368430305413</v>
+        <v>0.4563684303053676</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="U3" t="n">
-        <v>0.551189971614494</v>
+        <v>0.5511899716144729</v>
       </c>
       <c r="V3" t="n">
-        <v>0.553958541930814</v>
+        <v>0.5539585419308365</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6163497960168661</v>
+        <v>0.6163497960168799</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4686207682539599</v>
+        <v>0.4686207682539699</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7494393028908449</v>
+        <v>0.7494393028908003</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4801570100562864</v>
+        <v>0.480157010056269</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6163235236133492</v>
+        <v>0.6163235236133633</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7716502843614914</v>
+        <v>0.7716502843614921</v>
       </c>
     </row>
     <row r="4">
@@ -2133,82 +2133,82 @@
         <v>11.83203103056526</v>
       </c>
       <c r="C4" t="n">
-        <v>10.46104362126421</v>
+        <v>10.4610436212642</v>
       </c>
       <c r="D4" t="n">
-        <v>11.71768114607361</v>
+        <v>11.71768114607362</v>
       </c>
       <c r="E4" t="n">
-        <v>11.36910470072598</v>
+        <v>11.36910470072599</v>
       </c>
       <c r="F4" t="n">
         <v>11.25713897678464</v>
       </c>
       <c r="G4" t="n">
-        <v>12.61143690032774</v>
+        <v>12.61143690032775</v>
       </c>
       <c r="H4" t="n">
-        <v>12.39307946630158</v>
+        <v>12.3930794663016</v>
       </c>
       <c r="I4" t="n">
-        <v>11.19840840526318</v>
+        <v>11.19840840526319</v>
       </c>
       <c r="J4" t="n">
-        <v>12.72345707722379</v>
+        <v>12.72345707722377</v>
       </c>
       <c r="K4" t="n">
-        <v>12.10901185196909</v>
+        <v>12.10901185196911</v>
       </c>
       <c r="L4" t="n">
-        <v>12.99559396328342</v>
+        <v>12.99559396328334</v>
       </c>
       <c r="M4" t="n">
-        <v>14.41043887614852</v>
+        <v>14.41043887614853</v>
       </c>
       <c r="N4" t="n">
-        <v>12.8634312128291</v>
+        <v>12.86343121282912</v>
       </c>
       <c r="O4" t="n">
-        <v>12.70762414724329</v>
+        <v>12.7076241472433</v>
       </c>
       <c r="P4" t="n">
-        <v>13.59716134912112</v>
+        <v>13.59716134912117</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.02453927807818</v>
+        <v>12.02453927807821</v>
       </c>
       <c r="R4" t="n">
-        <v>11.87131959051047</v>
+        <v>11.87131959051048</v>
       </c>
       <c r="S4" t="n">
-        <v>12.43729544615981</v>
+        <v>12.43729544615982</v>
       </c>
       <c r="T4" t="n">
         <v>12.06702708466958</v>
       </c>
       <c r="U4" t="n">
-        <v>13.55452283662484</v>
+        <v>13.55452283662486</v>
       </c>
       <c r="V4" t="n">
-        <v>12.31052497168996</v>
+        <v>12.31052497169</v>
       </c>
       <c r="W4" t="n">
-        <v>14.25332627308069</v>
+        <v>14.2533262730807</v>
       </c>
       <c r="X4" t="n">
-        <v>12.26712641667662</v>
+        <v>12.26712641667667</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.39159759270292</v>
+        <v>14.39159759270295</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.51241906665743</v>
+        <v>12.51241906665744</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.02163724404747</v>
+        <v>12.0216372440475</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.71334256840738</v>
+        <v>14.71334256840743</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.821393561858288</v>
+        <v>9.821393561858299</v>
       </c>
       <c r="C5" t="n">
-        <v>9.850565720509524</v>
+        <v>9.850565720509461</v>
       </c>
       <c r="D5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="E5" t="n">
-        <v>9.816529950215141</v>
+        <v>9.816529950215132</v>
       </c>
       <c r="F5" t="n">
-        <v>9.81090134007021</v>
+        <v>9.810901340070208</v>
       </c>
       <c r="G5" t="n">
-        <v>9.880223197336901</v>
+        <v>9.880223197336912</v>
       </c>
       <c r="H5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="I5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="J5" t="n">
-        <v>9.8785307734097</v>
+        <v>9.878530773409691</v>
       </c>
       <c r="K5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="L5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="M5" t="n">
-        <v>9.873276426431232</v>
+        <v>9.873276426431215</v>
       </c>
       <c r="N5" t="n">
-        <v>9.83234875679943</v>
+        <v>9.832348756799433</v>
       </c>
       <c r="O5" t="n">
-        <v>9.842728497846656</v>
+        <v>9.842728497846643</v>
       </c>
       <c r="P5" t="n">
-        <v>9.840184172510122</v>
+        <v>9.84018417251011</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.811817793696303</v>
+        <v>9.81181779369633</v>
       </c>
       <c r="R5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="S5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="T5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="U5" t="n">
-        <v>9.846379132052713</v>
+        <v>9.846379132052688</v>
       </c>
       <c r="V5" t="n">
-        <v>9.956769276275729</v>
+        <v>9.956769276275715</v>
       </c>
       <c r="W5" t="n">
-        <v>9.870129122902085</v>
+        <v>9.870129122902101</v>
       </c>
       <c r="X5" t="n">
-        <v>9.816283627004337</v>
+        <v>9.816283627004371</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.918638685341753</v>
+        <v>9.918638685341712</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.820488451675899</v>
+        <v>9.820488451675885</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.870119546919515</v>
+        <v>9.870119546919497</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.936701311239974</v>
+        <v>9.936701311239968</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.369105770498899</v>
+        <v>2.369105770498916</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9981183611978488</v>
+        <v>0.9981183611978528</v>
       </c>
       <c r="D6" t="n">
-        <v>2.254755886007241</v>
+        <v>2.254755886007237</v>
       </c>
       <c r="E6" t="n">
-        <v>1.90617944065961</v>
+        <v>1.906179440659624</v>
       </c>
       <c r="F6" t="n">
-        <v>1.794213716718278</v>
+        <v>1.794213716718284</v>
       </c>
       <c r="G6" t="n">
-        <v>3.138974362647775</v>
+        <v>3.138974362647785</v>
       </c>
       <c r="H6" t="n">
-        <v>2.930154206235206</v>
+        <v>2.930154206235207</v>
       </c>
       <c r="I6" t="n">
-        <v>1.735483145196809</v>
+        <v>1.73548314519681</v>
       </c>
       <c r="J6" t="n">
-        <v>3.232484202911952</v>
+        <v>3.232484202911939</v>
       </c>
       <c r="K6" t="n">
-        <v>2.646086591902717</v>
+        <v>2.64608659190272</v>
       </c>
       <c r="L6" t="n">
-        <v>3.53266870321705</v>
+        <v>3.532668703217025</v>
       </c>
       <c r="M6" t="n">
-        <v>4.947513616082155</v>
+        <v>4.947513616082149</v>
       </c>
       <c r="N6" t="n">
-        <v>3.400505952762722</v>
+        <v>3.400505952762721</v>
       </c>
       <c r="O6" t="n">
-        <v>3.235161609563327</v>
+        <v>3.235161609563335</v>
       </c>
       <c r="P6" t="n">
-        <v>4.124698811441153</v>
+        <v>4.124698811441188</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.561614018011818</v>
+        <v>2.561614018011808</v>
       </c>
       <c r="R6" t="n">
-        <v>2.408394330444095</v>
+        <v>2.408394330444096</v>
       </c>
       <c r="S6" t="n">
-        <v>2.974370186093435</v>
+        <v>2.974370186093437</v>
       </c>
       <c r="T6" t="n">
-        <v>2.604101824603205</v>
+        <v>2.604101824603201</v>
       </c>
       <c r="U6" t="n">
-        <v>4.082060298944888</v>
+        <v>4.082060298944915</v>
       </c>
       <c r="V6" t="n">
-        <v>2.712711448765814</v>
+        <v>2.7127114487658</v>
       </c>
       <c r="W6" t="n">
-        <v>4.780863735400732</v>
+        <v>4.780863735400756</v>
       </c>
       <c r="X6" t="n">
-        <v>2.794663878996662</v>
+        <v>2.794663878996685</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.928672332636555</v>
+        <v>4.928672332636554</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.049493806591057</v>
+        <v>3.049493806591066</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.558711983981101</v>
+        <v>2.558711983981111</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.250417308341029</v>
+        <v>5.250417308341061</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3584683017919175</v>
+        <v>0.3584683017918925</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3876404604431431</v>
+        <v>0.3876404604430387</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3536046901487714</v>
+        <v>0.3536046901487719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3479760800038323</v>
+        <v>0.3479760800038331</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4077606596569488</v>
+        <v>0.4077606596569673</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3875578990978685</v>
+        <v>0.3875578990978626</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4103511663648525</v>
+        <v>0.4103511663648534</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3694234967330646</v>
+        <v>0.3694234967330571</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3702659601667132</v>
+        <v>0.3702659601666855</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3677216348301598</v>
+        <v>0.3677216348301634</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3488925336299348</v>
+        <v>0.3488925336299038</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3739165943727546</v>
+        <v>0.3739165943727388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3589557533515751</v>
+        <v>0.3589557533515935</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3976665852221294</v>
+        <v>0.397666585222153</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3438210893243818</v>
+        <v>0.3438210893244188</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4557134252753896</v>
+        <v>0.4557134252753725</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.357563191609525</v>
+        <v>0.3575631916095354</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4071942868531431</v>
+        <v>0.4071942868531825</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4737760511736069</v>
+        <v>0.4737760511736078</v>
       </c>
     </row>
   </sheetData>
@@ -2638,82 +2638,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.88155320348719</v>
+        <v>4.881553203487237</v>
       </c>
       <c r="C2" t="n">
-        <v>3.164121933695939</v>
+        <v>3.164121933695941</v>
       </c>
       <c r="D2" t="n">
-        <v>6.508360996310378</v>
+        <v>6.508360996310397</v>
       </c>
       <c r="E2" t="n">
-        <v>4.099216325343753</v>
+        <v>4.099216325343749</v>
       </c>
       <c r="F2" t="n">
-        <v>4.592942467843786</v>
+        <v>4.592942467843793</v>
       </c>
       <c r="G2" t="n">
-        <v>7.683985716794859</v>
+        <v>7.683985716794881</v>
       </c>
       <c r="H2" t="n">
-        <v>6.87352804320382</v>
+        <v>6.873528043203833</v>
       </c>
       <c r="I2" t="n">
-        <v>4.846471307448255</v>
+        <v>4.84647130744825</v>
       </c>
       <c r="J2" t="n">
-        <v>7.777993706817854</v>
+        <v>7.777993706817867</v>
       </c>
       <c r="K2" t="n">
-        <v>5.072061771755763</v>
+        <v>5.072061771755764</v>
       </c>
       <c r="L2" t="n">
-        <v>8.001820162268629</v>
+        <v>8.001820162268618</v>
       </c>
       <c r="M2" t="n">
         <v>11.72392600212417</v>
       </c>
       <c r="N2" t="n">
-        <v>7.044040618155581</v>
+        <v>7.044040618155583</v>
       </c>
       <c r="O2" t="n">
-        <v>8.054425182805513</v>
+        <v>8.054425182805508</v>
       </c>
       <c r="P2" t="n">
-        <v>10.40787461044069</v>
+        <v>10.4078746104407</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.615067190059283</v>
+        <v>5.615067190059297</v>
       </c>
       <c r="R2" t="n">
-        <v>5.365466095898332</v>
+        <v>5.365466095898336</v>
       </c>
       <c r="S2" t="n">
-        <v>7.108983474642371</v>
+        <v>7.108983474642377</v>
       </c>
       <c r="T2" t="n">
-        <v>6.581572300225292</v>
+        <v>6.581572300225297</v>
       </c>
       <c r="U2" t="n">
-        <v>8.791907319236905</v>
+        <v>8.791907319236895</v>
       </c>
       <c r="V2" t="n">
-        <v>6.743441737754312</v>
+        <v>6.743441737754337</v>
       </c>
       <c r="W2" t="n">
-        <v>11.60605508169298</v>
+        <v>11.60605508169293</v>
       </c>
       <c r="X2" t="n">
-        <v>8.358948775242208</v>
+        <v>8.358948775242204</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.7087141903936</v>
+        <v>12.70871419039362</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.805855125559326</v>
+        <v>6.805855125559329</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.355811215328927</v>
+        <v>6.355811215328922</v>
       </c>
       <c r="AB2" t="n">
         <v>12.94294753134518</v>
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4479726512710178</v>
+        <v>0.4479726512710395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5560385171209236</v>
+        <v>0.5560385171209238</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4798770161918225</v>
+        <v>0.4798770161918232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.452661884626984</v>
+        <v>0.4526618846269844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5963374217291417</v>
+        <v>0.5963374217291525</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5616410415648565</v>
+        <v>0.5616410415648805</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5733979438315724</v>
+        <v>0.5733979438315731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4756009880728509</v>
+        <v>0.4756009880728548</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5017780650788823</v>
+        <v>0.5017780650789189</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4953614309868</v>
+        <v>0.4953614309868051</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4238231450924963</v>
+        <v>0.4238231450925196</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5106475598601526</v>
+        <v>0.510647559860209</v>
       </c>
       <c r="V3" t="n">
-        <v>0.51407536821735</v>
+        <v>0.5140753682173739</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5708807785981903</v>
+        <v>0.5708807785982061</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4350857056821724</v>
+        <v>0.435085705682197</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6926421288955814</v>
+        <v>0.692642128895559</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.445690018319134</v>
+        <v>0.4456900183191325</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5708566285402098</v>
+        <v>0.5708566285402122</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.714749022348683</v>
+        <v>0.7147490223486767</v>
       </c>
     </row>
     <row r="4">
@@ -2814,31 +2814,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.35242069357295</v>
+        <v>11.35242069357297</v>
       </c>
       <c r="C4" t="n">
-        <v>10.71702007902019</v>
+        <v>10.7170200790202</v>
       </c>
       <c r="D4" t="n">
-        <v>11.94537303111543</v>
+        <v>11.94537303111544</v>
       </c>
       <c r="E4" t="n">
-        <v>11.05103233962065</v>
+        <v>11.05103233962067</v>
       </c>
       <c r="F4" t="n">
-        <v>11.23803936704834</v>
+        <v>11.23803936704835</v>
       </c>
       <c r="G4" t="n">
-        <v>12.37387443684958</v>
+        <v>12.37387443684959</v>
       </c>
       <c r="H4" t="n">
         <v>12.07847213170013</v>
       </c>
       <c r="I4" t="n">
-        <v>11.33963375441917</v>
+        <v>11.33963375441918</v>
       </c>
       <c r="J4" t="n">
-        <v>12.42322389822388</v>
+        <v>12.42322389822392</v>
       </c>
       <c r="K4" t="n">
         <v>11.42185882964229</v>
@@ -2847,19 +2847,19 @@
         <v>12.48972136002428</v>
       </c>
       <c r="M4" t="n">
-        <v>13.84800026718729</v>
+        <v>13.8480002671873</v>
       </c>
       <c r="N4" t="n">
-        <v>12.1406219630103</v>
+        <v>12.14062196301031</v>
       </c>
       <c r="O4" t="n">
-        <v>12.50889527229062</v>
+        <v>12.50889527229063</v>
       </c>
       <c r="P4" t="n">
-        <v>13.36669995306521</v>
+        <v>13.36669995306522</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.61977792832237</v>
+        <v>11.61977792832239</v>
       </c>
       <c r="R4" t="n">
         <v>11.52880126046473</v>
@@ -2868,31 +2868,31 @@
         <v>12.16429287160221</v>
       </c>
       <c r="T4" t="n">
-        <v>11.97205769170185</v>
+        <v>11.97205769170188</v>
       </c>
       <c r="U4" t="n">
-        <v>12.77769885106739</v>
+        <v>12.77769885106741</v>
       </c>
       <c r="V4" t="n">
-        <v>12.15619435502538</v>
+        <v>12.15619435502545</v>
       </c>
       <c r="W4" t="n">
         <v>13.80342266509122</v>
       </c>
       <c r="X4" t="n">
-        <v>12.61989054583724</v>
+        <v>12.61989054583725</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.20532896213562</v>
+        <v>14.20532896213563</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.05380614787423</v>
+        <v>12.05380614787424</v>
       </c>
       <c r="AA4" t="n">
         <v>11.88977042727766</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.30057363740704</v>
+        <v>14.30057363740706</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.736432644021471</v>
+        <v>9.736432644021496</v>
       </c>
       <c r="C5" t="n">
-        <v>9.766404299340294</v>
+        <v>9.766404299340303</v>
       </c>
       <c r="D5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="E5" t="n">
-        <v>9.731825661862707</v>
+        <v>9.7318256618627</v>
       </c>
       <c r="F5" t="n">
-        <v>9.728955712095015</v>
+        <v>9.728955712095031</v>
       </c>
       <c r="G5" t="n">
-        <v>9.790509860666347</v>
+        <v>9.7905098606664</v>
       </c>
       <c r="H5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="I5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="J5" t="n">
-        <v>9.79294809043045</v>
+        <v>9.792948090430473</v>
       </c>
       <c r="K5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="L5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="M5" t="n">
-        <v>9.783763726050772</v>
+        <v>9.783763726050793</v>
       </c>
       <c r="N5" t="n">
-        <v>9.74650284835743</v>
+        <v>9.746502848357466</v>
       </c>
       <c r="O5" t="n">
-        <v>9.756044085539394</v>
+        <v>9.756044085539406</v>
       </c>
       <c r="P5" t="n">
-        <v>9.753705297760723</v>
+        <v>9.753705297760735</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.727630432597227</v>
+        <v>9.72763043259723</v>
       </c>
       <c r="R5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="S5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="T5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="U5" t="n">
-        <v>9.759276912236285</v>
+        <v>9.759276912236313</v>
       </c>
       <c r="V5" t="n">
-        <v>9.885663462242208</v>
+        <v>9.885663462242201</v>
       </c>
       <c r="W5" t="n">
-        <v>9.781231213172127</v>
+        <v>9.78123121317217</v>
       </c>
       <c r="X5" t="n">
-        <v>9.731735503680506</v>
+        <v>9.73173550368054</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.82561179556156</v>
+        <v>9.825611795561576</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.735600651114549</v>
+        <v>9.735600651114563</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.781222410759582</v>
+        <v>9.781222410759614</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.843538871634307</v>
+        <v>9.843538871634319</v>
       </c>
     </row>
     <row r="6">
@@ -2996,79 +2996,79 @@
         <v>1.314434913130641</v>
       </c>
       <c r="D6" t="n">
-        <v>2.542787865225872</v>
+        <v>2.542787865225876</v>
       </c>
       <c r="E6" t="n">
-        <v>1.648447173731107</v>
+        <v>1.648447173731105</v>
       </c>
       <c r="F6" t="n">
-        <v>1.835454201158785</v>
+        <v>1.835454201158789</v>
       </c>
       <c r="G6" t="n">
-        <v>2.962506619267788</v>
+        <v>2.962506619267782</v>
       </c>
       <c r="H6" t="n">
-        <v>2.675886965810577</v>
+        <v>2.675886965810574</v>
       </c>
       <c r="I6" t="n">
-        <v>1.937048588529618</v>
+        <v>1.937048588529613</v>
       </c>
       <c r="J6" t="n">
-        <v>2.991240386463289</v>
+        <v>2.991240386463312</v>
       </c>
       <c r="K6" t="n">
-        <v>2.019273663752733</v>
+        <v>2.019273663752729</v>
       </c>
       <c r="L6" t="n">
-        <v>3.087136194134719</v>
+        <v>3.087136194134713</v>
       </c>
       <c r="M6" t="n">
-        <v>4.445415101297737</v>
+        <v>4.445415101297745</v>
       </c>
       <c r="N6" t="n">
-        <v>2.738036797120743</v>
+        <v>2.738036797120742</v>
       </c>
       <c r="O6" t="n">
-        <v>3.097527454708833</v>
+        <v>3.097527454708831</v>
       </c>
       <c r="P6" t="n">
-        <v>3.95533213548342</v>
+        <v>3.955332135483411</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.217192762432818</v>
+        <v>2.21719276243282</v>
       </c>
       <c r="R6" t="n">
-        <v>2.126216094575196</v>
+        <v>2.126216094575173</v>
       </c>
       <c r="S6" t="n">
-        <v>2.761707705712658</v>
+        <v>2.761707705712654</v>
       </c>
       <c r="T6" t="n">
-        <v>2.569472525812321</v>
+        <v>2.569472525812322</v>
       </c>
       <c r="U6" t="n">
-        <v>3.366331033485605</v>
+        <v>3.366331033485598</v>
       </c>
       <c r="V6" t="n">
-        <v>2.60558688044149</v>
+        <v>2.605586880441517</v>
       </c>
       <c r="W6" t="n">
-        <v>4.392054847509439</v>
+        <v>4.392054847509417</v>
       </c>
       <c r="X6" t="n">
-        <v>3.208522728255452</v>
+        <v>3.208522728255439</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.802743796246069</v>
+        <v>4.802743796246073</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65122098198468</v>
+        <v>2.651220981984671</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.487185261388101</v>
+        <v>2.487185261388095</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.897988471517507</v>
+        <v>4.897988471517501</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3338474781319365</v>
+        <v>0.3338474781319282</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3638191334507487</v>
+        <v>0.3638191334507491</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3292404959731511</v>
+        <v>0.3292404959731512</v>
       </c>
       <c r="F7" t="n">
-        <v>0.32637054620547</v>
+        <v>0.3263705462054702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3791420430845641</v>
+        <v>0.3791420430846</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3609645786698549</v>
+        <v>0.3609645786698601</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="M7" t="n">
-        <v>0.381178560161233</v>
+        <v>0.3811785601612334</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3439176824678786</v>
+        <v>0.3439176824679086</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3446762679576036</v>
+        <v>0.3446762679576111</v>
       </c>
       <c r="P7" t="n">
-        <v>0.342337480178935</v>
+        <v>0.3423374801789327</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3250452667076765</v>
+        <v>0.3250452667076751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3479090946544922</v>
+        <v>0.3479090946545049</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3350559876583083</v>
+        <v>0.335055987658322</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3698633955903394</v>
+        <v>0.369863395590365</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3203676860987173</v>
+        <v>0.320367686098734</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4230266296720086</v>
+        <v>0.4230266296720049</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3330154852250004</v>
+        <v>0.333015485225002</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3786372448700213</v>
+        <v>0.3786372448700508</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4409537057447639</v>
+        <v>0.4409537057447593</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.526506404365988</v>
+        <v>4.526506404365898</v>
       </c>
       <c r="C2" t="n">
-        <v>3.314593860909163</v>
+        <v>3.314593860909162</v>
       </c>
       <c r="D2" t="n">
-        <v>5.063184638485652</v>
+        <v>5.063184638485567</v>
       </c>
       <c r="E2" t="n">
         <v>2.364168832517626</v>
       </c>
       <c r="F2" t="n">
-        <v>5.859781575752886</v>
+        <v>5.859781575752893</v>
       </c>
       <c r="G2" t="n">
-        <v>7.110094078724556</v>
+        <v>7.110094078724469</v>
       </c>
       <c r="H2" t="n">
-        <v>6.388905766023943</v>
+        <v>6.388905766023845</v>
       </c>
       <c r="I2" t="n">
-        <v>5.797596833397221</v>
+        <v>5.797596833397122</v>
       </c>
       <c r="J2" t="n">
-        <v>7.272249403240533</v>
+        <v>7.272249403240492</v>
       </c>
       <c r="K2" t="n">
-        <v>6.908855262737183</v>
+        <v>6.908855262737103</v>
       </c>
       <c r="L2" t="n">
-        <v>8.120881044235595</v>
+        <v>8.120881044235528</v>
       </c>
       <c r="M2" t="n">
-        <v>10.74960675053977</v>
+        <v>10.74960675053986</v>
       </c>
       <c r="N2" t="n">
-        <v>6.247805158847713</v>
+        <v>6.247805158847624</v>
       </c>
       <c r="O2" t="n">
-        <v>6.600011553658043</v>
+        <v>6.60001155365795</v>
       </c>
       <c r="P2" t="n">
-        <v>9.298989542704607</v>
+        <v>9.298989542704513</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.19916409614058</v>
+        <v>6.199164096140477</v>
       </c>
       <c r="R2" t="n">
-        <v>5.699760160444739</v>
+        <v>5.699760160444649</v>
       </c>
       <c r="S2" t="n">
-        <v>7.533436293022296</v>
+        <v>7.533436293022209</v>
       </c>
       <c r="T2" t="n">
-        <v>6.9390794833472</v>
+        <v>6.939079483347109</v>
       </c>
       <c r="U2" t="n">
-        <v>8.314235536454603</v>
+        <v>8.314235536454513</v>
       </c>
       <c r="V2" t="n">
-        <v>6.240664720825141</v>
+        <v>6.240664720825129</v>
       </c>
       <c r="W2" t="n">
-        <v>10.95771152264174</v>
+        <v>10.95771152264163</v>
       </c>
       <c r="X2" t="n">
-        <v>8.770992774129972</v>
+        <v>8.770992774129898</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.56144580525049</v>
+        <v>11.56144580525046</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.099833417800167</v>
+        <v>5.099833417800136</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.909274555941759</v>
+        <v>6.909274555941663</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.79702462852514</v>
+        <v>11.79702462852516</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4185926293768636</v>
+        <v>0.4185926293767915</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5238795500517904</v>
+        <v>0.5238795500517909</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4486079650747239</v>
+        <v>0.4486079650747237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4311065143029267</v>
+        <v>0.4311065143029265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5583101147390828</v>
+        <v>0.558310114738949</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5268276877582186</v>
+        <v>0.5268276877582</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="M3" t="n">
-        <v>0.538576451067431</v>
+        <v>0.5385764510674987</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4446106775363248</v>
+        <v>0.4446106775362751</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4692620510571419</v>
+        <v>0.4692620510570575</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4632194037544715</v>
+        <v>0.4632194037543448</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3958506518447712</v>
+        <v>0.3958506518447196</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4771367583814679</v>
+        <v>0.4771367583813798</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4828983971562254</v>
+        <v>0.482898397156218</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5343371853703234</v>
+        <v>0.534337185370248</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4064567859029772</v>
+        <v>0.4064567859029378</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6481843607948398</v>
+        <v>0.6481843607947746</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4164430372926397</v>
+        <v>0.4164430372925467</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5343144428658236</v>
+        <v>0.5343144428657141</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.67128609978145</v>
+        <v>0.6712860997814498</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.13898958207222</v>
+        <v>11.13898958207214</v>
       </c>
       <c r="C4" t="n">
-        <v>10.69063019406181</v>
+        <v>10.69063019406178</v>
       </c>
       <c r="D4" t="n">
-        <v>11.33460249641484</v>
+        <v>11.33460249641476</v>
       </c>
       <c r="E4" t="n">
-        <v>10.33553470538355</v>
+        <v>10.33553470538353</v>
       </c>
       <c r="F4" t="n">
-        <v>11.62144837365645</v>
+        <v>11.62144837365643</v>
       </c>
       <c r="G4" t="n">
-        <v>12.08067695135774</v>
+        <v>12.08067695135766</v>
       </c>
       <c r="H4" t="n">
-        <v>11.8178122799991</v>
+        <v>11.81781227999902</v>
       </c>
       <c r="I4" t="n">
-        <v>11.60228711755671</v>
+        <v>11.60228711755663</v>
       </c>
       <c r="J4" t="n">
-        <v>12.15828419909313</v>
+        <v>12.15828419909308</v>
       </c>
       <c r="K4" t="n">
-        <v>12.00732776599585</v>
+        <v>12.00732776599575</v>
       </c>
       <c r="L4" t="n">
-        <v>12.44909693102669</v>
+        <v>12.44909693102664</v>
       </c>
       <c r="M4" t="n">
-        <v>13.40994513917787</v>
+        <v>13.4099451391779</v>
       </c>
       <c r="N4" t="n">
-        <v>11.76638276557035</v>
+        <v>11.76638276557027</v>
       </c>
       <c r="O4" t="n">
-        <v>11.89475786066241</v>
+        <v>11.89475786066232</v>
       </c>
       <c r="P4" t="n">
-        <v>12.87850364467022</v>
+        <v>12.87850364467015</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.74865366938579</v>
+        <v>11.74865366938571</v>
       </c>
       <c r="R4" t="n">
-        <v>11.56662679912175</v>
+        <v>11.56662679912167</v>
       </c>
       <c r="S4" t="n">
-        <v>12.23498021733404</v>
+        <v>12.23498021733393</v>
       </c>
       <c r="T4" t="n">
-        <v>12.01834413949747</v>
+        <v>12.01834413949738</v>
       </c>
       <c r="U4" t="n">
-        <v>12.51957237295747</v>
+        <v>12.51957237295738</v>
       </c>
       <c r="V4" t="n">
-        <v>11.90688815583283</v>
+        <v>11.90688815583284</v>
       </c>
       <c r="W4" t="n">
-        <v>13.48308832866043</v>
+        <v>13.48308832866035</v>
       </c>
       <c r="X4" t="n">
-        <v>12.68605502257584</v>
+        <v>12.68605502257578</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.70314238526543</v>
+        <v>13.70314238526539</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.34796054612331</v>
+        <v>11.34796054612323</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.0074805934453</v>
+        <v>12.00748059344522</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.79923383120147</v>
+        <v>13.79923383120146</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.641703248647655</v>
+        <v>9.641703248647564</v>
       </c>
       <c r="C5" t="n">
-        <v>9.673447597976237</v>
+        <v>9.673447597976214</v>
       </c>
       <c r="D5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="E5" t="n">
-        <v>9.637335262851973</v>
+        <v>9.63733526285195</v>
       </c>
       <c r="F5" t="n">
-        <v>9.642760060478937</v>
+        <v>9.642760060478924</v>
       </c>
       <c r="G5" t="n">
-        <v>9.692628631416641</v>
+        <v>9.692628631416525</v>
       </c>
       <c r="H5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="I5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="J5" t="n">
-        <v>9.699657192540689</v>
+        <v>9.699657192540641</v>
       </c>
       <c r="K5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="L5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="M5" t="n">
-        <v>9.688144498991672</v>
+        <v>9.688144498991729</v>
       </c>
       <c r="N5" t="n">
-        <v>9.651186521682479</v>
+        <v>9.651186521682346</v>
       </c>
       <c r="O5" t="n">
-        <v>9.660171657859721</v>
+        <v>9.660171657859633</v>
       </c>
       <c r="P5" t="n">
-        <v>9.657969183874194</v>
+        <v>9.657969183874139</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.633414064887033</v>
+        <v>9.63341406488691</v>
       </c>
       <c r="R5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="S5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="T5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="U5" t="n">
-        <v>9.66304189620999</v>
+        <v>9.663041896209867</v>
       </c>
       <c r="V5" t="n">
-        <v>9.808249941961202</v>
+        <v>9.808249941961229</v>
       </c>
       <c r="W5" t="n">
-        <v>9.683890780166079</v>
+        <v>9.683890780165987</v>
       </c>
       <c r="X5" t="n">
-        <v>9.637279876207664</v>
+        <v>9.637279876207609</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.725386738747282</v>
+        <v>9.725386738747195</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.640919747574761</v>
+        <v>9.640919747574639</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.683882490790225</v>
+        <v>9.683882490790134</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.744032782492173</v>
+        <v>9.744032782492166</v>
       </c>
     </row>
     <row r="6">
@@ -3674,82 +3674,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.80854642716853</v>
+        <v>1.808546427168429</v>
       </c>
       <c r="C6" t="n">
-        <v>1.360187039158081</v>
+        <v>1.360187039158083</v>
       </c>
       <c r="D6" t="n">
-        <v>2.004159341511148</v>
+        <v>2.004159341511052</v>
       </c>
       <c r="E6" t="n">
-        <v>1.005091550479821</v>
+        <v>1.005091550479822</v>
       </c>
       <c r="F6" t="n">
-        <v>2.291005218752727</v>
+        <v>2.291005218752725</v>
       </c>
       <c r="G6" t="n">
-        <v>2.741822060964191</v>
+        <v>2.741822060964081</v>
       </c>
       <c r="H6" t="n">
-        <v>2.487369125095411</v>
+        <v>2.48736912509531</v>
       </c>
       <c r="I6" t="n">
-        <v>2.27184396265302</v>
+        <v>2.271843962652921</v>
       </c>
       <c r="J6" t="n">
-        <v>2.796474053867698</v>
+        <v>2.796474053867665</v>
       </c>
       <c r="K6" t="n">
-        <v>2.676884611092138</v>
+        <v>2.676884611092048</v>
       </c>
       <c r="L6" t="n">
-        <v>3.118653776123021</v>
+        <v>3.118653776122935</v>
       </c>
       <c r="M6" t="n">
-        <v>4.07950198427415</v>
+        <v>4.079501984274128</v>
       </c>
       <c r="N6" t="n">
-        <v>2.435939610666662</v>
+        <v>2.435939610666563</v>
       </c>
       <c r="O6" t="n">
-        <v>2.555902970268851</v>
+        <v>2.555902970268749</v>
       </c>
       <c r="P6" t="n">
-        <v>3.539648754276663</v>
+        <v>3.539648754276562</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.418210514482102</v>
+        <v>2.418210514482</v>
       </c>
       <c r="R6" t="n">
-        <v>2.236183644218057</v>
+        <v>2.236183644217958</v>
       </c>
       <c r="S6" t="n">
-        <v>2.904537062430346</v>
+        <v>2.904537062430221</v>
       </c>
       <c r="T6" t="n">
-        <v>2.687900984593775</v>
+        <v>2.687900984593676</v>
       </c>
       <c r="U6" t="n">
-        <v>3.180717482563898</v>
+        <v>3.180717482563803</v>
       </c>
       <c r="V6" t="n">
-        <v>2.413279684083646</v>
+        <v>2.413279684083641</v>
       </c>
       <c r="W6" t="n">
-        <v>4.144233438266869</v>
+        <v>4.144233438266766</v>
       </c>
       <c r="X6" t="n">
-        <v>3.347200132182219</v>
+        <v>3.347200132182198</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.372699230361749</v>
+        <v>4.372699230361684</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.017517391219641</v>
+        <v>2.017517391219518</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.677037438541619</v>
+        <v>2.67703743854152</v>
       </c>
       <c r="AB6" t="n">
         <v>4.468790676297744</v>
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3112600937438629</v>
+        <v>0.3112600937438598</v>
       </c>
       <c r="C7" t="n">
         <v>0.3430044430725079</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3068921079482468</v>
+        <v>0.3068921079482464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3123169055752223</v>
+        <v>0.3123169055752219</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3537737410229964</v>
+        <v>0.3537737410229422</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3378470473152472</v>
+        <v>0.3378470473152272</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3577013440879497</v>
+        <v>0.3577013440879126</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3207433667786924</v>
+        <v>0.3207433667786451</v>
       </c>
       <c r="O7" t="n">
-        <v>0.321316767466141</v>
+        <v>0.3213167674660499</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3191142934806412</v>
+        <v>0.3191142934805578</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3029709099832711</v>
+        <v>0.3029709099832025</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3241870058164202</v>
+        <v>0.3241870058162831</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3146414702120314</v>
+        <v>0.3146414702120348</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3450358897724808</v>
+        <v>0.3450358897724002</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2984249858141282</v>
+        <v>0.2984249858140313</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3949435838435773</v>
+        <v>0.3949435838434891</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3104765926710385</v>
+        <v>0.3104765926709372</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3534393358865456</v>
+        <v>0.3534393358864314</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4135896275884587</v>
+        <v>0.4135896275884584</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.512627039766631</v>
+        <v>1.512627039766633</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8978030003448976</v>
+        <v>0.897803000344897</v>
       </c>
       <c r="D2" t="n">
-        <v>2.387364547904477</v>
+        <v>2.387364547904482</v>
       </c>
       <c r="E2" t="n">
-        <v>3.490953306725335</v>
+        <v>3.490953306725339</v>
       </c>
       <c r="F2" t="n">
-        <v>1.777954994435971</v>
+        <v>1.777954994435972</v>
       </c>
       <c r="G2" t="n">
-        <v>4.68501665065081</v>
+        <v>4.685016650650809</v>
       </c>
       <c r="H2" t="n">
-        <v>4.428942941489065</v>
+        <v>4.428942941489066</v>
       </c>
       <c r="I2" t="n">
-        <v>2.64392605687086</v>
+        <v>2.643926056870863</v>
       </c>
       <c r="J2" t="n">
-        <v>5.51566706968266</v>
+        <v>5.515667069682664</v>
       </c>
       <c r="K2" t="n">
-        <v>3.847471256694989</v>
+        <v>3.847471256694995</v>
       </c>
       <c r="L2" t="n">
-        <v>4.696279126165649</v>
+        <v>4.696279126165648</v>
       </c>
       <c r="M2" t="n">
-        <v>6.458363981423448</v>
+        <v>6.458363981423444</v>
       </c>
       <c r="N2" t="n">
-        <v>7.295045217136683</v>
+        <v>7.295045217136684</v>
       </c>
       <c r="O2" t="n">
-        <v>7.608758841502696</v>
+        <v>7.608758841502702</v>
       </c>
       <c r="P2" t="n">
-        <v>9.887666592242621</v>
+        <v>9.887666592242633</v>
       </c>
       <c r="Q2" t="n">
         <v>4.255471338153081</v>
       </c>
       <c r="R2" t="n">
-        <v>2.843900748677543</v>
+        <v>2.843900748677544</v>
       </c>
       <c r="S2" t="n">
-        <v>3.855047450008256</v>
+        <v>3.85504745000826</v>
       </c>
       <c r="T2" t="n">
-        <v>5.106309011374494</v>
+        <v>5.106309011374496</v>
       </c>
       <c r="U2" t="n">
-        <v>7.696992709910794</v>
+        <v>7.696992709910812</v>
       </c>
       <c r="V2" t="n">
         <v>5.823177882786489</v>
       </c>
       <c r="W2" t="n">
-        <v>13.86709991729165</v>
+        <v>13.86709991729167</v>
       </c>
       <c r="X2" t="n">
-        <v>4.703617807583516</v>
+        <v>4.703617807583524</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.2957418015282</v>
+        <v>11.29574180152821</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.406163492865597</v>
+        <v>5.406163492865606</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.743598657258456</v>
+        <v>4.743598657258453</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.45305221054951</v>
+        <v>8.453052210549515</v>
       </c>
     </row>
     <row r="3">
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3825963856448068</v>
+        <v>0.382596385644816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.476654139534056</v>
+        <v>0.4766541395340557</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="E3" t="n">
         <v>0.4150983748277469</v>
@@ -4109,70 +4109,70 @@
         <v>0.3840343870816372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5116090340717556</v>
+        <v>0.5116090340717716</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4831708648928682</v>
+        <v>0.4831708648928693</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4857861372197931</v>
+        <v>0.4857861372197934</v>
       </c>
       <c r="N3" t="n">
-        <v>0.406620989940413</v>
+        <v>0.4066209899404176</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4293836311053205</v>
+        <v>0.4293836311053282</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4238039577422261</v>
+        <v>0.423803957742235</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3615968468723798</v>
+        <v>0.3615968468723847</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4369188120318136</v>
+        <v>0.4369188120318144</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4449306713307051</v>
+        <v>0.4449306713306985</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4894728561712149</v>
+        <v>0.4894728561712243</v>
       </c>
       <c r="X3" t="n">
-        <v>0.371390362971586</v>
+        <v>0.37139036297159</v>
       </c>
       <c r="Y3" t="n">
         <v>0.5950486312820157</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3806114904337222</v>
+        <v>0.3806114904337243</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4894518561718915</v>
+        <v>0.4894518561718996</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6099930672872758</v>
+        <v>0.609993067287275</v>
       </c>
     </row>
     <row r="4">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.880719750993139</v>
+        <v>9.880719750993142</v>
       </c>
       <c r="C4" t="n">
-        <v>9.648490509050575</v>
+        <v>9.648490509050571</v>
       </c>
       <c r="D4" t="n">
         <v>10.19955130102297</v>
@@ -4200,16 +4200,16 @@
         <v>11.03701851208083</v>
       </c>
       <c r="H4" t="n">
-        <v>10.94368265206069</v>
+        <v>10.9436826520607</v>
       </c>
       <c r="I4" t="n">
-        <v>10.29306495834387</v>
+        <v>10.29306495834389</v>
       </c>
       <c r="J4" t="n">
-        <v>11.37607269646234</v>
+        <v>11.37607269646235</v>
       </c>
       <c r="K4" t="n">
-        <v>10.7317430509385</v>
+        <v>10.73174305093851</v>
       </c>
       <c r="L4" t="n">
         <v>11.04112355215533</v>
@@ -4224,22 +4224,22 @@
         <v>12.10268820833218</v>
       </c>
       <c r="P4" t="n">
-        <v>12.933323323191</v>
+        <v>12.93332332319101</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.88045428965113</v>
+        <v>10.88045428965114</v>
       </c>
       <c r="R4" t="n">
-        <v>10.36595338528602</v>
+        <v>10.36595338528603</v>
       </c>
       <c r="S4" t="n">
         <v>10.73450448443704</v>
       </c>
       <c r="T4" t="n">
-        <v>11.19057463049995</v>
+        <v>11.19057463049996</v>
       </c>
       <c r="U4" t="n">
-        <v>12.13484841727254</v>
+        <v>12.13484841727255</v>
       </c>
       <c r="V4" t="n">
         <v>11.71115915675144</v>
@@ -4248,16 +4248,16 @@
         <v>14.38378004130603</v>
       </c>
       <c r="X4" t="n">
-        <v>11.04379841535699</v>
+        <v>11.043798415357</v>
       </c>
       <c r="Y4" t="n">
         <v>13.4465502025217</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.29986806793436</v>
+        <v>11.29986806793438</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.05837096558467</v>
+        <v>11.05837096558466</v>
       </c>
       <c r="AB4" t="n">
         <v>12.41609309590582</v>
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.468836847055615</v>
+        <v>9.468836847055636</v>
       </c>
       <c r="C5" t="n">
-        <v>9.494986694664625</v>
+        <v>9.494986694664634</v>
       </c>
       <c r="D5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="E5" t="n">
-        <v>9.469589886874108</v>
+        <v>9.469589886874104</v>
       </c>
       <c r="F5" t="n">
-        <v>9.459695590362617</v>
+        <v>9.459695590362621</v>
       </c>
       <c r="G5" t="n">
-        <v>9.515860442464243</v>
+        <v>9.515860442464254</v>
       </c>
       <c r="H5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="I5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="J5" t="n">
-        <v>9.541786924370459</v>
+        <v>9.541786924370461</v>
       </c>
       <c r="K5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="L5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="M5" t="n">
-        <v>9.504118692350268</v>
+        <v>9.504118692350273</v>
       </c>
       <c r="N5" t="n">
-        <v>9.47759353321022</v>
+        <v>9.477593533210229</v>
       </c>
       <c r="O5" t="n">
-        <v>9.485890248622402</v>
+        <v>9.485890248622415</v>
       </c>
       <c r="P5" t="n">
-        <v>9.483856523201391</v>
+        <v>9.483856523201393</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.461182761762107</v>
+        <v>9.461182761762116</v>
       </c>
       <c r="R5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="S5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="T5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="U5" t="n">
-        <v>9.488636733587546</v>
+        <v>9.488636733587542</v>
       </c>
       <c r="V5" t="n">
-        <v>9.750851202743108</v>
+        <v>9.750851202743103</v>
       </c>
       <c r="W5" t="n">
         <v>9.507792065555616</v>
       </c>
       <c r="X5" t="n">
-        <v>9.464752383379</v>
+        <v>9.464752383378997</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.546273195850166</v>
+        <v>9.54627319585018</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.468113376058994</v>
+        <v>9.468113376059014</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.507784411302458</v>
+        <v>9.507784411302454</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.557390136037016</v>
+        <v>9.557390136037018</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6961675676988404</v>
+        <v>0.6961675676988397</v>
       </c>
       <c r="C6" t="n">
-        <v>0.463938325756273</v>
+        <v>0.4639383257562733</v>
       </c>
       <c r="D6" t="n">
-        <v>1.014999117728672</v>
+        <v>1.014999117728671</v>
       </c>
       <c r="E6" t="n">
-        <v>1.40615070774432</v>
+        <v>1.406150707744319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7832111002068017</v>
+        <v>0.7832111002068021</v>
       </c>
       <c r="G6" t="n">
-        <v>1.843901843167142</v>
+        <v>1.843901843167135</v>
       </c>
       <c r="H6" t="n">
-        <v>1.759130468766388</v>
+        <v>1.7591304687664</v>
       </c>
       <c r="I6" t="n">
-        <v>1.108512775049572</v>
+        <v>1.108512775049585</v>
       </c>
       <c r="J6" t="n">
-        <v>2.142985176698723</v>
+        <v>2.142985176698731</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5471908676442</v>
+        <v>1.547190867644201</v>
       </c>
       <c r="L6" t="n">
-        <v>1.856571368861032</v>
+        <v>1.856571368861028</v>
       </c>
       <c r="M6" t="n">
-        <v>2.496500999718257</v>
+        <v>2.496500999718258</v>
       </c>
       <c r="N6" t="n">
-        <v>2.803791092767832</v>
+        <v>2.803791092767829</v>
       </c>
       <c r="O6" t="n">
-        <v>2.909571539418485</v>
+        <v>2.909571539418488</v>
       </c>
       <c r="P6" t="n">
-        <v>3.740206654277311</v>
+        <v>3.740206654277312</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69590210635683</v>
+        <v>1.695902106356832</v>
       </c>
       <c r="R6" t="n">
         <v>1.181401201991721</v>
       </c>
       <c r="S6" t="n">
-        <v>1.549952301142733</v>
+        <v>1.549952301142735</v>
       </c>
       <c r="T6" t="n">
-        <v>2.00602244720565</v>
+        <v>2.006022447205652</v>
       </c>
       <c r="U6" t="n">
-        <v>2.941731748358845</v>
+        <v>2.941731748358847</v>
       </c>
       <c r="V6" t="n">
-        <v>2.249732382437754</v>
+        <v>2.249732382437755</v>
       </c>
       <c r="W6" t="n">
-        <v>5.19066337239234</v>
+        <v>5.190663372392339</v>
       </c>
       <c r="X6" t="n">
-        <v>1.8506817464433</v>
+        <v>1.850681746443302</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.261998019227399</v>
+        <v>4.261998019227402</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.115315884640066</v>
+        <v>2.115315884640067</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87381878229037</v>
+        <v>1.873818782290368</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.23154091261152</v>
+        <v>3.231540912611517</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2842846637613267</v>
+        <v>0.2842846637613382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3104345113703267</v>
+        <v>0.3104345113703268</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="E7" t="n">
         <v>0.2850377035798053</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2751434070683157</v>
+        <v>0.2751434070683161</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3227437735505496</v>
+        <v>0.3227437735505611</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3086994046068386</v>
+        <v>0.3086994046068385</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3195665090559665</v>
+        <v>0.3195665090559667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2930413499159264</v>
+        <v>0.2930413499159248</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2927735797087118</v>
+        <v>0.2927735797087223</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2907398542876974</v>
+        <v>0.2907398542877009</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2766305784678078</v>
+        <v>0.2766305784678129</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2955200646738577</v>
+        <v>0.2955200646738548</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2894244284294167</v>
+        <v>0.2894244284294138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3146753966419276</v>
+        <v>0.3146753966419283</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2716357144653043</v>
+        <v>0.271635714465299</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3617210125558645</v>
+        <v>0.3617210125558745</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2835611927646989</v>
+        <v>0.283561192764707</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3232322280081629</v>
+        <v>0.3232322280081647</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3728379527427167</v>
+        <v>0.3728379527427171</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5427103015456741</v>
+        <v>0.5427103015456685</v>
       </c>
       <c r="C2" t="n">
-        <v>1.141680994567019</v>
+        <v>1.141680994567017</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9001688408397132</v>
+        <v>0.9001688408397068</v>
       </c>
       <c r="E2" t="n">
-        <v>1.408194328359947</v>
+        <v>1.408194328359945</v>
       </c>
       <c r="F2" t="n">
-        <v>2.002378446293963</v>
+        <v>2.002378446293964</v>
       </c>
       <c r="G2" t="n">
-        <v>3.897569876269148</v>
+        <v>3.897569876269117</v>
       </c>
       <c r="H2" t="n">
-        <v>3.63396568755916</v>
+        <v>3.633965687559151</v>
       </c>
       <c r="I2" t="n">
-        <v>1.912244813698274</v>
+        <v>1.912244813698275</v>
       </c>
       <c r="J2" t="n">
-        <v>3.730732011124489</v>
+        <v>3.73073201112448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.601847606845431</v>
+        <v>1.601847606845423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.89205062287417</v>
+        <v>0.8920506228741599</v>
       </c>
       <c r="M2" t="n">
-        <v>2.760777106838034</v>
+        <v>2.760777106838029</v>
       </c>
       <c r="N2" t="n">
-        <v>5.561750521158105</v>
+        <v>5.561750521158098</v>
       </c>
       <c r="O2" t="n">
-        <v>6.555392329758191</v>
+        <v>6.555392329758173</v>
       </c>
       <c r="P2" t="n">
-        <v>8.517003757795745</v>
+        <v>8.51700375779572</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.999607353231888</v>
+        <v>1.999607353231879</v>
       </c>
       <c r="R2" t="n">
-        <v>1.166937416725598</v>
+        <v>1.166937416725585</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61127681906918</v>
+        <v>2.611276819069178</v>
       </c>
       <c r="T2" t="n">
-        <v>3.50874802991186</v>
+        <v>3.508748029911865</v>
       </c>
       <c r="U2" t="n">
-        <v>4.014893419883268</v>
+        <v>4.014893419883259</v>
       </c>
       <c r="V2" t="n">
-        <v>4.298204240803956</v>
+        <v>4.298204240803939</v>
       </c>
       <c r="W2" t="n">
-        <v>8.871165676564669</v>
+        <v>8.871165676564647</v>
       </c>
       <c r="X2" t="n">
-        <v>6.926897138375814</v>
+        <v>6.926897138375796</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.028934823538295</v>
+        <v>9.028934823538275</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.538704384284046</v>
+        <v>2.538704384284031</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.431302735745687</v>
+        <v>5.431302735745682</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.455822692425141</v>
+        <v>5.455822692425144</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3180177588651295</v>
+        <v>0.3180177588651407</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4022763107716493</v>
+        <v>0.4022763107716419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3472102075549765</v>
+        <v>0.3472102075549753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3260459088431993</v>
+        <v>0.3260459088431983</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4253113277643892</v>
+        <v>0.4253113277644094</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40325438162373</v>
+        <v>0.403254381623716</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4013717936132697</v>
+        <v>0.4013717936132685</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3379978582430164</v>
+        <v>0.3379978582430128</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3569284440297433</v>
+        <v>0.356928444029726</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3522881000333061</v>
+        <v>0.3522881000333127</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3005534599159261</v>
+        <v>0.3005534599159334</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3630632412680075</v>
+        <v>0.3630632412680023</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3737794670622658</v>
+        <v>0.3737794670622453</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4069017411335299</v>
+        <v>0.4069017411335242</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3086982527547016</v>
+        <v>0.3086982527546855</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4944784450611262</v>
+        <v>0.4944784450611138</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3163670176878178</v>
+        <v>0.3163670176878031</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4068842764428214</v>
+        <v>0.406884276442786</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5067999656333576</v>
+        <v>0.5067999656333558</v>
       </c>
     </row>
     <row r="4">
@@ -4866,58 +4866,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.373063379053747</v>
+        <v>9.373063379053749</v>
       </c>
       <c r="C4" t="n">
-        <v>9.588452746897559</v>
+        <v>9.588452746897563</v>
       </c>
       <c r="D4" t="n">
-        <v>9.503352819136339</v>
+        <v>9.503352819136341</v>
       </c>
       <c r="E4" t="n">
-        <v>9.680670224822881</v>
+        <v>9.680670224822883</v>
       </c>
       <c r="F4" t="n">
         <v>9.901399004696941</v>
       </c>
       <c r="G4" t="n">
-        <v>10.59587029929035</v>
+        <v>10.59587029929036</v>
       </c>
       <c r="H4" t="n">
         <v>10.49978966790225</v>
       </c>
       <c r="I4" t="n">
-        <v>9.872242626847211</v>
+        <v>9.872242626847195</v>
       </c>
       <c r="J4" t="n">
         <v>10.57011224596943</v>
       </c>
       <c r="K4" t="n">
-        <v>9.759106489817356</v>
+        <v>9.75910648981735</v>
       </c>
       <c r="L4" t="n">
-        <v>9.500393824016825</v>
+        <v>9.500393824016824</v>
       </c>
       <c r="M4" t="n">
         <v>10.17801943615841</v>
       </c>
       <c r="N4" t="n">
-        <v>11.20244460255666</v>
+        <v>11.20244460255664</v>
       </c>
       <c r="O4" t="n">
-        <v>11.56461537386017</v>
+        <v>11.56461537386016</v>
       </c>
       <c r="P4" t="n">
         <v>12.2795997049755</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.904085246644458</v>
+        <v>9.904085246644499</v>
       </c>
       <c r="R4" t="n">
         <v>9.600586832491963</v>
       </c>
       <c r="S4" t="n">
-        <v>10.12703158435667</v>
+        <v>10.12703158435666</v>
       </c>
       <c r="T4" t="n">
         <v>10.45414930206978</v>
@@ -4926,19 +4926,19 @@
         <v>10.63863335325511</v>
       </c>
       <c r="V4" t="n">
-        <v>10.98585945185225</v>
+        <v>10.98585945185224</v>
       </c>
       <c r="W4" t="n">
-        <v>12.40868756558756</v>
+        <v>12.40868756558757</v>
       </c>
       <c r="X4" t="n">
-        <v>11.70002451417159</v>
+        <v>11.70002451417158</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.46619256704059</v>
+        <v>12.4661925670406</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.10057978406603</v>
+        <v>10.10057978406602</v>
       </c>
       <c r="AA4" t="n">
         <v>11.15489791656905</v>
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.291165585719733</v>
+        <v>9.291165585719694</v>
       </c>
       <c r="C5" t="n">
-        <v>9.318948422182311</v>
+        <v>9.318948422182306</v>
       </c>
       <c r="D5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="E5" t="n">
-        <v>9.293953971494021</v>
+        <v>9.293953971494028</v>
       </c>
       <c r="F5" t="n">
-        <v>9.290395479286621</v>
+        <v>9.290395479286616</v>
       </c>
       <c r="G5" t="n">
-        <v>9.330272831678837</v>
+        <v>9.330272831678819</v>
       </c>
       <c r="H5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="I5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="J5" t="n">
-        <v>9.357285723231454</v>
+        <v>9.357285723231447</v>
       </c>
       <c r="K5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="L5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="M5" t="n">
-        <v>9.318043905023965</v>
+        <v>9.318043905023963</v>
       </c>
       <c r="N5" t="n">
-        <v>9.298448097324796</v>
+        <v>9.29844809732481</v>
       </c>
       <c r="O5" t="n">
-        <v>9.305348073549892</v>
+        <v>9.305348073549919</v>
       </c>
       <c r="P5" t="n">
-        <v>9.303656722652866</v>
+        <v>9.303656722652885</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.284800053828917</v>
+        <v>9.284800053828905</v>
       </c>
       <c r="R5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="S5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="T5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="U5" t="n">
-        <v>9.307584135104813</v>
+        <v>9.307584135104836</v>
       </c>
       <c r="V5" t="n">
-        <v>9.55545270474571</v>
+        <v>9.55545270474569</v>
       </c>
       <c r="W5" t="n">
-        <v>9.323562753528158</v>
+        <v>9.323562753528153</v>
       </c>
       <c r="X5" t="n">
-        <v>9.287768735177671</v>
+        <v>9.287768735177639</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.355483433732186</v>
+        <v>9.355483433732164</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.290563909944593</v>
+        <v>9.29056390994459</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.323556387853468</v>
+        <v>9.323556387853451</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.364478469914799</v>
+        <v>9.364478469914793</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3185438260392552</v>
+        <v>0.3185438260392464</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5339331938830656</v>
+        <v>0.5339331938830586</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4488332661218448</v>
+        <v>0.4488332661218326</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6261506718083747</v>
+        <v>0.626150671808374</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8468794516824351</v>
+        <v>0.8468794516824354</v>
       </c>
       <c r="G6" t="n">
-        <v>1.533838708918589</v>
+        <v>1.53383870891857</v>
       </c>
       <c r="H6" t="n">
-        <v>1.445270114887755</v>
+        <v>1.445270114887741</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8177230738326859</v>
+        <v>0.8177230738326904</v>
       </c>
       <c r="J6" t="n">
-        <v>1.470997223930083</v>
+        <v>1.470997223930079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7045869368028623</v>
+        <v>0.7045869368028497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4458742710023297</v>
+        <v>0.4458742710023195</v>
       </c>
       <c r="M6" t="n">
-        <v>1.123499883143904</v>
+        <v>1.123499883143902</v>
       </c>
       <c r="N6" t="n">
-        <v>2.147925049542136</v>
+        <v>2.14792504954214</v>
       </c>
       <c r="O6" t="n">
-        <v>2.502583783488372</v>
+        <v>2.502583783488369</v>
       </c>
       <c r="P6" t="n">
-        <v>3.217568114603714</v>
+        <v>3.217568114603711</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8495656936299665</v>
+        <v>0.8495656936299893</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5460672794774722</v>
+        <v>0.5460672794774618</v>
       </c>
       <c r="S6" t="n">
-        <v>1.072512031342145</v>
+        <v>1.072512031342149</v>
       </c>
       <c r="T6" t="n">
-        <v>1.399629749055287</v>
+        <v>1.399629749055278</v>
       </c>
       <c r="U6" t="n">
-        <v>1.576601762883322</v>
+        <v>1.576601762883318</v>
       </c>
       <c r="V6" t="n">
-        <v>1.674976119074223</v>
+        <v>1.674976119074225</v>
       </c>
       <c r="W6" t="n">
-        <v>3.346655975215774</v>
+        <v>3.346655975215763</v>
       </c>
       <c r="X6" t="n">
-        <v>2.637992923799801</v>
+        <v>2.63799292379978</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.411673014026101</v>
+        <v>3.411673014026088</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.046060231051531</v>
+        <v>1.046060231051518</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.100378363554559</v>
+        <v>2.100378363554548</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.113819586456969</v>
+        <v>2.113819586456966</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2366460327052339</v>
+        <v>0.2366460327051881</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2644288691678128</v>
+        <v>0.2644288691678023</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="E7" t="n">
-        <v>0.239434418479523</v>
+        <v>0.2394344184795221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2358759262721142</v>
+        <v>0.2358759262721137</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2682412413070427</v>
+        <v>0.2682412413070234</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2581707011921055</v>
+        <v>0.2581707011920894</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2635243520094582</v>
+        <v>0.2635243520094574</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2439285443103154</v>
+        <v>0.2439285443103033</v>
       </c>
       <c r="O7" t="n">
-        <v>0.243316483178121</v>
+        <v>0.2433164831781179</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2416251322810784</v>
+        <v>0.2416251322810873</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2302805008143868</v>
+        <v>0.2302805008143987</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2455525447330271</v>
+        <v>0.2455525447330409</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2445693719677045</v>
+        <v>0.2445693719676957</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2615311631563696</v>
+        <v>0.2615311631563604</v>
       </c>
       <c r="X7" t="n">
-        <v>0.225737144805855</v>
+        <v>0.2257371448058428</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3009638807176706</v>
+        <v>0.3009638807176607</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2360443569300999</v>
+        <v>0.2360443569300837</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2690368348389565</v>
+        <v>0.2690368348389482</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3099589169002888</v>
+        <v>0.309958916900288</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5091221180107776</v>
+        <v>0.5091221180107723</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8525660262632881</v>
+        <v>0.8525660262632884</v>
       </c>
       <c r="D2" t="n">
-        <v>1.385667274965817</v>
+        <v>1.385667274965798</v>
       </c>
       <c r="E2" t="n">
         <v>0.5261162840614859</v>
       </c>
       <c r="F2" t="n">
-        <v>2.781038829774095</v>
+        <v>2.781038829774096</v>
       </c>
       <c r="G2" t="n">
-        <v>2.332203354310904</v>
+        <v>2.332203354310896</v>
       </c>
       <c r="H2" t="n">
-        <v>3.494609222740162</v>
+        <v>3.494609222740171</v>
       </c>
       <c r="I2" t="n">
-        <v>1.733618647067132</v>
+        <v>1.733618647067126</v>
       </c>
       <c r="J2" t="n">
-        <v>2.745912028774535</v>
+        <v>2.74591202877455</v>
       </c>
       <c r="K2" t="n">
-        <v>1.740078637433892</v>
+        <v>1.740078637433885</v>
       </c>
       <c r="L2" t="n">
-        <v>1.011976127919807</v>
+        <v>1.011976127919803</v>
       </c>
       <c r="M2" t="n">
-        <v>2.695574394259252</v>
+        <v>2.695574394259287</v>
       </c>
       <c r="N2" t="n">
-        <v>3.882353568810166</v>
+        <v>3.882353568810158</v>
       </c>
       <c r="O2" t="n">
-        <v>4.943443021491493</v>
+        <v>4.943443021491485</v>
       </c>
       <c r="P2" t="n">
-        <v>7.466334173200494</v>
+        <v>7.466334173200497</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.408606819971967</v>
+        <v>1.408606819971961</v>
       </c>
       <c r="R2" t="n">
-        <v>1.031314781674352</v>
+        <v>1.031314781674347</v>
       </c>
       <c r="S2" t="n">
-        <v>3.43132117546475</v>
+        <v>3.431321175464723</v>
       </c>
       <c r="T2" t="n">
-        <v>3.143001833520683</v>
+        <v>3.143001833520676</v>
       </c>
       <c r="U2" t="n">
-        <v>3.981195007759444</v>
+        <v>3.98119500775943</v>
       </c>
       <c r="V2" t="n">
-        <v>3.002621633477736</v>
+        <v>3.002621633477739</v>
       </c>
       <c r="W2" t="n">
-        <v>5.310543827447629</v>
+        <v>5.310543827447622</v>
       </c>
       <c r="X2" t="n">
         <v>7.577780775605062</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.366304852822056</v>
+        <v>6.366304852822048</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.293640296708119</v>
+        <v>1.293640296708104</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.748324942311507</v>
+        <v>5.74832494231151</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.643063347221347</v>
+        <v>4.643063347221343</v>
       </c>
     </row>
     <row r="3">
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2805345444725604</v>
+        <v>0.2805345444725614</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3583125851821358</v>
+        <v>0.3583125851821356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="E3" t="n">
         <v>0.3080853275878619</v>
@@ -5477,70 +5477,70 @@
         <v>0.2938530180457646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3768947557213962</v>
+        <v>0.3768947557213888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3577997676454139</v>
+        <v>0.3577997676454213</v>
       </c>
       <c r="K3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3584462032505077</v>
+        <v>0.358446203250543</v>
       </c>
       <c r="N3" t="n">
-        <v>0.298478645099695</v>
+        <v>0.2984786450996805</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3154801789703604</v>
+        <v>0.315480178970324</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3113126922099255</v>
+        <v>0.3113126922099168</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2648498808576805</v>
+        <v>0.2648498808576623</v>
       </c>
       <c r="R3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="S3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="T3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3209141988895161</v>
+        <v>0.3209141988895188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3318380450795791</v>
+        <v>0.3318380450795789</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3603611305063187</v>
+        <v>0.3603611305062895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2721647084559657</v>
+        <v>0.2721647084559649</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.438884265015505</v>
+        <v>0.4388842650154807</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2790520160204255</v>
+        <v>0.2790520160204236</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.360345445484982</v>
+        <v>0.3603454454849691</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4520206515774911</v>
+        <v>0.4520206515774921</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.244459222334484</v>
+        <v>9.244459222334468</v>
       </c>
       <c r="C4" t="n">
         <v>9.368348587377032</v>
       </c>
       <c r="D4" t="n">
-        <v>9.563949639131701</v>
+        <v>9.563949639131671</v>
       </c>
       <c r="E4" t="n">
-        <v>9.244448788774291</v>
+        <v>9.244448788774285</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07310852956978</v>
+        <v>10.07310852956977</v>
       </c>
       <c r="G4" t="n">
-        <v>9.908950925265184</v>
+        <v>9.90895092526516</v>
       </c>
       <c r="H4" t="n">
-        <v>10.3326342146488</v>
+        <v>10.33263421464878</v>
       </c>
       <c r="I4" t="n">
-        <v>9.690773828411331</v>
+        <v>9.690773828411317</v>
       </c>
       <c r="J4" t="n">
-        <v>10.09386998695522</v>
+        <v>10.09386998695521</v>
       </c>
       <c r="K4" t="n">
-        <v>9.693128419042978</v>
+        <v>9.693128419042937</v>
       </c>
       <c r="L4" t="n">
-        <v>9.427743604136426</v>
+        <v>9.42774360413641</v>
       </c>
       <c r="M4" t="n">
-        <v>10.04018841166623</v>
+        <v>10.04018841166626</v>
       </c>
       <c r="N4" t="n">
-        <v>10.47396247566732</v>
+        <v>10.4739624756673</v>
       </c>
       <c r="O4" t="n">
-        <v>10.86071712122823</v>
+        <v>10.86071712122822</v>
       </c>
       <c r="P4" t="n">
-        <v>11.78028132074254</v>
+        <v>11.78028132074253</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.572310833916708</v>
+        <v>9.572310833916688</v>
       </c>
       <c r="R4" t="n">
-        <v>9.434792316344016</v>
+        <v>9.434792316343998</v>
       </c>
       <c r="S4" t="n">
-        <v>10.30956646458267</v>
+        <v>10.30956646458264</v>
       </c>
       <c r="T4" t="n">
-        <v>10.20447745006071</v>
+        <v>10.20447745006069</v>
       </c>
       <c r="U4" t="n">
-        <v>10.50998901950955</v>
+        <v>10.50998901950952</v>
       </c>
       <c r="V4" t="n">
-        <v>10.38787275416302</v>
+        <v>10.38787275416303</v>
       </c>
       <c r="W4" t="n">
-        <v>10.99452105428394</v>
+        <v>10.99452105428393</v>
       </c>
       <c r="X4" t="n">
-        <v>11.82090229864694</v>
+        <v>11.82090229864692</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.37933355066104</v>
+        <v>11.37933355066103</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.530406886192099</v>
+        <v>9.530406886192088</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.15408712996644</v>
+        <v>11.15408712996641</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.75651084721827</v>
+        <v>10.75651084721826</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.161141735990622</v>
+        <v>9.161141735990604</v>
       </c>
       <c r="C5" t="n">
-        <v>9.188199011919878</v>
+        <v>9.188199011919879</v>
       </c>
       <c r="D5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="E5" t="n">
-        <v>9.16497906538841</v>
+        <v>9.164979065388408</v>
       </c>
       <c r="F5" t="n">
-        <v>9.166558507205158</v>
+        <v>9.166558507205147</v>
       </c>
       <c r="G5" t="n">
-        <v>9.196263901472078</v>
+        <v>9.196263901472083</v>
       </c>
       <c r="H5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="I5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="J5" t="n">
-        <v>9.223431110403647</v>
+        <v>9.223431110403626</v>
       </c>
       <c r="K5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="L5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="M5" t="n">
-        <v>9.188332629988341</v>
+        <v>9.188332629988373</v>
       </c>
       <c r="N5" t="n">
-        <v>9.167682149958917</v>
+        <v>9.167682149958889</v>
       </c>
       <c r="O5" t="n">
-        <v>9.17387900941268</v>
+        <v>9.173879009412678</v>
       </c>
       <c r="P5" t="n">
-        <v>9.172360009425635</v>
+        <v>9.17236000942561</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.15542486028161</v>
+        <v>9.155424860281585</v>
       </c>
       <c r="R5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="S5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="T5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="U5" t="n">
-        <v>9.175859645863749</v>
+        <v>9.175859645863733</v>
       </c>
       <c r="V5" t="n">
-        <v>9.414403498116178</v>
+        <v>9.414403498116185</v>
       </c>
       <c r="W5" t="n">
-        <v>9.190237589228808</v>
+        <v>9.190237589228792</v>
       </c>
       <c r="X5" t="n">
-        <v>9.158091029046153</v>
+        <v>9.158091029046117</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.218858349692209</v>
+        <v>9.218858349692191</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.160601371778535</v>
+        <v>9.160601371778524</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.190231872222716</v>
+        <v>9.190231872222711</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.228924998364114</v>
+        <v>9.228924998364104</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2910629249140722</v>
+        <v>0.2910629249140431</v>
       </c>
       <c r="C6" t="n">
-        <v>0.414952289956599</v>
+        <v>0.4149522899565988</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6105533417112814</v>
+        <v>0.6105533417112484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2910524913538637</v>
+        <v>0.2910524913538636</v>
       </c>
       <c r="F6" t="n">
-        <v>1.119712232149351</v>
+        <v>1.119712232149352</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9485173441780077</v>
+        <v>0.9485173441780046</v>
       </c>
       <c r="H6" t="n">
-        <v>1.379237917228381</v>
+        <v>1.379237917228355</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7373775309909164</v>
+        <v>0.737377530990887</v>
       </c>
       <c r="J6" t="n">
-        <v>1.097949194312599</v>
+        <v>1.097949194312592</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7397321216225627</v>
+        <v>0.7397321216225174</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4743473067160086</v>
+        <v>0.4743473067159792</v>
       </c>
       <c r="M6" t="n">
-        <v>1.086792114245797</v>
+        <v>1.086792114245827</v>
       </c>
       <c r="N6" t="n">
-        <v>1.520566178246905</v>
+        <v>1.520566178246876</v>
       </c>
       <c r="O6" t="n">
-        <v>1.900283540141071</v>
+        <v>1.90028354014106</v>
       </c>
       <c r="P6" t="n">
-        <v>2.819847739655382</v>
+        <v>2.819847739655372</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6189145364962857</v>
+        <v>0.618914536496259</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4813960189236008</v>
+        <v>0.4813960189235729</v>
       </c>
       <c r="S6" t="n">
-        <v>1.356170167162257</v>
+        <v>1.356170167162216</v>
       </c>
       <c r="T6" t="n">
-        <v>1.251081152640292</v>
+        <v>1.251081152640266</v>
       </c>
       <c r="U6" t="n">
-        <v>1.549555438422388</v>
+        <v>1.549555438422366</v>
       </c>
       <c r="V6" t="n">
-        <v>1.189330748274841</v>
+        <v>1.189330748274842</v>
       </c>
       <c r="W6" t="n">
-        <v>2.03408747319678</v>
+        <v>2.034087473196769</v>
       </c>
       <c r="X6" t="n">
-        <v>2.860468717559779</v>
+        <v>2.86046871755976</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.42593725324063</v>
+        <v>2.425937253240597</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5770105887716794</v>
+        <v>0.5770105887716586</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.20069083254602</v>
+        <v>2.200690832545976</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.803114549797847</v>
+        <v>1.803114549797841</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2077454385701789</v>
+        <v>0.2077454385701811</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2348027144994466</v>
+        <v>0.2348027144994464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2115827679679803</v>
+        <v>0.2115827679679802</v>
       </c>
       <c r="F7" t="n">
         <v>0.2131622097847249</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2358303203849114</v>
+        <v>0.2358303203849255</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2275103177610126</v>
+        <v>0.2275103177610114</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2349363325679143</v>
+        <v>0.2349363325679442</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2142858525385097</v>
+        <v>0.2142858525384781</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2134454283255216</v>
+        <v>0.2134454283255223</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2119264283384738</v>
+        <v>0.2119264283384571</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2020285628611709</v>
+        <v>0.2020285628611669</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2154260647765866</v>
+        <v>0.2154260647765754</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2158614922280043</v>
+        <v>0.2158614922280042</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2298040081416388</v>
+        <v>0.229804008141636</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1976574479589868</v>
+        <v>0.1976574479589576</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2654620522718007</v>
+        <v>0.2654620522717689</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2072050743580965</v>
+        <v>0.2072050743580987</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2368355748022834</v>
+        <v>0.2368355748022821</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2755287009436856</v>
+        <v>0.2755287009436829</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.135220183003155</v>
+        <v>4.135220183003237</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346207393587784</v>
+        <v>1.346207393587883</v>
       </c>
       <c r="D2" t="n">
-        <v>4.151778673766964</v>
+        <v>4.151778673767064</v>
       </c>
       <c r="E2" t="n">
-        <v>4.153039599786138</v>
+        <v>4.153039599786192</v>
       </c>
       <c r="F2" t="n">
-        <v>2.952410114697927</v>
+        <v>2.952410114697925</v>
       </c>
       <c r="G2" t="n">
-        <v>7.902497429271604</v>
+        <v>7.902497429271699</v>
       </c>
       <c r="H2" t="n">
-        <v>6.775217548383077</v>
+        <v>6.775217548383161</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857200663301284</v>
+        <v>3.857200663301358</v>
       </c>
       <c r="J2" t="n">
-        <v>7.727920857338933</v>
+        <v>7.727920857338961</v>
       </c>
       <c r="K2" t="n">
-        <v>4.976076503648827</v>
+        <v>4.976076503648907</v>
       </c>
       <c r="L2" t="n">
-        <v>8.195804755803724</v>
+        <v>8.195804755803811</v>
       </c>
       <c r="M2" t="n">
         <v>12.78407008598498</v>
       </c>
       <c r="N2" t="n">
-        <v>7.50441995568864</v>
+        <v>7.504419955688716</v>
       </c>
       <c r="O2" t="n">
-        <v>7.296350547609145</v>
+        <v>7.296350547609222</v>
       </c>
       <c r="P2" t="n">
-        <v>9.804614211222482</v>
+        <v>9.804614211222535</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.981948362624697</v>
+        <v>4.981948362624775</v>
       </c>
       <c r="R2" t="n">
-        <v>4.684255024258367</v>
+        <v>4.684255024258308</v>
       </c>
       <c r="S2" t="n">
-        <v>5.840849136777378</v>
+        <v>5.840849136777456</v>
       </c>
       <c r="T2" t="n">
-        <v>5.274856577147221</v>
+        <v>5.274856577147301</v>
       </c>
       <c r="U2" t="n">
-        <v>9.527703860906115</v>
+        <v>9.527703860906223</v>
       </c>
       <c r="V2" t="n">
-        <v>6.765173746895747</v>
+        <v>6.765173746895746</v>
       </c>
       <c r="W2" t="n">
-        <v>12.91641936683842</v>
+        <v>12.91641936683851</v>
       </c>
       <c r="X2" t="n">
-        <v>6.779492825103619</v>
+        <v>6.779492825103718</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.85470474484664</v>
+        <v>12.85470474484672</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.096748986628763</v>
+        <v>7.096748986628834</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.941892442054268</v>
+        <v>5.941892442054351</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.57495000584854</v>
+        <v>12.57495000584855</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4542948741190225</v>
+        <v>0.4542948741191384</v>
       </c>
       <c r="C3" t="n">
-        <v>0.560271021200596</v>
+        <v>0.5602710212006113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4876951537200002</v>
+        <v>0.4876951537200489</v>
       </c>
       <c r="F3" t="n">
-        <v>0.454205024103952</v>
+        <v>0.4542050241039525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6046170165649581</v>
+        <v>0.6046170165649803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5699793248956194</v>
+        <v>0.5699793248956342</v>
       </c>
       <c r="K3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="L3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5848998596192057</v>
+        <v>0.5848998596192064</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4822877107390471</v>
+        <v>0.4822877107391198</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5088101411331095</v>
+        <v>0.5088101411331468</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5023088525818983</v>
+        <v>0.502308852582003</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4298267642306788</v>
+        <v>0.4298267642306979</v>
       </c>
       <c r="R3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="S3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5179542835081926</v>
+        <v>0.5179542835082027</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5224505990823096</v>
+        <v>0.5224505990823307</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5788245246845873</v>
+        <v>0.5788245246847115</v>
       </c>
       <c r="X3" t="n">
-        <v>0.441237911435146</v>
+        <v>0.4412379114352733</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7024619323925224</v>
+        <v>0.7024619323925778</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4519821264598801</v>
+        <v>0.451982126459901</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.578800056033427</v>
+        <v>0.5788000560335099</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7237215383633075</v>
+        <v>0.7237215383633088</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.08721755503858</v>
+        <v>11.08721755503874</v>
       </c>
       <c r="C4" t="n">
-        <v>10.05887972432315</v>
+        <v>10.05887972432329</v>
       </c>
       <c r="D4" t="n">
-        <v>11.09325293048235</v>
+        <v>11.09325293048257</v>
       </c>
       <c r="E4" t="n">
-        <v>11.07794575290804</v>
+        <v>11.07794575290814</v>
       </c>
       <c r="F4" t="n">
-        <v>10.64371340052225</v>
+        <v>10.6437134005223</v>
       </c>
       <c r="G4" t="n">
-        <v>12.46034587370056</v>
+        <v>12.46034587370069</v>
       </c>
       <c r="H4" t="n">
-        <v>12.04946559430535</v>
+        <v>12.04946559430549</v>
       </c>
       <c r="I4" t="n">
-        <v>10.98588270477727</v>
+        <v>10.98588270477748</v>
       </c>
       <c r="J4" t="n">
         <v>12.41329434490997</v>
       </c>
       <c r="K4" t="n">
-        <v>11.39369981008049</v>
+        <v>11.39369981008064</v>
       </c>
       <c r="L4" t="n">
-        <v>12.56725295003296</v>
+        <v>12.56725295003311</v>
       </c>
       <c r="M4" t="n">
-        <v>14.24349828155856</v>
+        <v>14.24349828155866</v>
       </c>
       <c r="N4" t="n">
-        <v>12.31525130904125</v>
+        <v>12.31525130904139</v>
       </c>
       <c r="O4" t="n">
-        <v>12.23941245307062</v>
+        <v>12.23941245307076</v>
       </c>
       <c r="P4" t="n">
-        <v>13.15364510493871</v>
+        <v>13.15364510493884</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.39584003372636</v>
+        <v>11.39584003372652</v>
       </c>
       <c r="R4" t="n">
-        <v>11.2873343075835</v>
+        <v>11.28733430758363</v>
       </c>
       <c r="S4" t="n">
-        <v>11.70889928018291</v>
+        <v>11.70889928018305</v>
       </c>
       <c r="T4" t="n">
-        <v>11.50260163841791</v>
+        <v>11.50260163841807</v>
       </c>
       <c r="U4" t="n">
-        <v>13.05271453389387</v>
+        <v>13.05271453389403</v>
       </c>
       <c r="V4" t="n">
-        <v>12.17968916549916</v>
+        <v>12.17968916549914</v>
       </c>
       <c r="W4" t="n">
-        <v>14.28786154349971</v>
+        <v>14.28786154349991</v>
       </c>
       <c r="X4" t="n">
-        <v>12.05102388246716</v>
+        <v>12.05102388246732</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.26536728847337</v>
+        <v>14.26536728847355</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.16666002793313</v>
+        <v>12.1666600279333</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.74572837844595</v>
+        <v>11.74572837844612</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.17284711315683</v>
+        <v>14.1728471131569</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.745563503557548</v>
+        <v>9.745563503557761</v>
       </c>
       <c r="C5" t="n">
-        <v>9.772415145518885</v>
+        <v>9.772415145518963</v>
       </c>
       <c r="D5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="E5" t="n">
-        <v>9.741970742964448</v>
+        <v>9.741970742964599</v>
       </c>
       <c r="F5" t="n">
-        <v>9.733146980405996</v>
+        <v>9.733146980406026</v>
       </c>
       <c r="G5" t="n">
-        <v>9.800354159307382</v>
+        <v>9.800354159307554</v>
       </c>
       <c r="H5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="I5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="J5" t="n">
-        <v>9.804308709127506</v>
+        <v>9.804308709127675</v>
       </c>
       <c r="K5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="L5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="M5" t="n">
-        <v>9.797043983937417</v>
+        <v>9.797043983937478</v>
       </c>
       <c r="N5" t="n">
-        <v>9.755766563797076</v>
+        <v>9.755766563797202</v>
       </c>
       <c r="O5" t="n">
-        <v>9.765433678233613</v>
+        <v>9.765433678233642</v>
       </c>
       <c r="P5" t="n">
-        <v>9.763064034898679</v>
+        <v>9.763064034898782</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.736645164822301</v>
+        <v>9.736645164822475</v>
       </c>
       <c r="R5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="S5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="T5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="U5" t="n">
-        <v>9.768766610753392</v>
+        <v>9.768766610753577</v>
       </c>
       <c r="V5" t="n">
-        <v>9.904289883877416</v>
+        <v>9.904289883877437</v>
       </c>
       <c r="W5" t="n">
-        <v>9.790953098887709</v>
+        <v>9.790953098887842</v>
       </c>
       <c r="X5" t="n">
-        <v>9.740804393981898</v>
+        <v>9.740804393982115</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.836017482173528</v>
+        <v>9.836017482173574</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.744720534193458</v>
+        <v>9.744720534193656</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.790944180351701</v>
+        <v>9.790944180351831</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.853213500909217</v>
+        <v>9.853213500909309</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.680715156858167</v>
+        <v>1.680715156858264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6523773261427926</v>
+        <v>0.6523773261428011</v>
       </c>
       <c r="D6" t="n">
-        <v>1.686750532301951</v>
+        <v>1.686750532302065</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671443354727631</v>
+        <v>1.671443354727672</v>
       </c>
       <c r="F6" t="n">
-        <v>1.237211002341836</v>
+        <v>1.237211002341835</v>
       </c>
       <c r="G6" t="n">
-        <v>3.044547900168882</v>
+        <v>3.044547900168961</v>
       </c>
       <c r="H6" t="n">
-        <v>2.642963196124942</v>
+        <v>2.642963196125034</v>
       </c>
       <c r="I6" t="n">
-        <v>1.579380306596866</v>
+        <v>1.579380306596956</v>
       </c>
       <c r="J6" t="n">
-        <v>2.975654904553932</v>
+        <v>2.975654904554001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.987197411900094</v>
+        <v>1.987197411900171</v>
       </c>
       <c r="L6" t="n">
-        <v>3.160750551852581</v>
+        <v>3.160750551852662</v>
       </c>
       <c r="M6" t="n">
         <v>4.836995883378153</v>
       </c>
       <c r="N6" t="n">
-        <v>2.908748910860843</v>
+        <v>2.908748910860932</v>
       </c>
       <c r="O6" t="n">
-        <v>2.823614479538942</v>
+        <v>2.823614479539038</v>
       </c>
       <c r="P6" t="n">
-        <v>3.737847131407023</v>
+        <v>3.737847131407065</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.989337635545948</v>
+        <v>1.98933763554604</v>
       </c>
       <c r="R6" t="n">
-        <v>1.880831909403089</v>
+        <v>1.880831909403194</v>
       </c>
       <c r="S6" t="n">
-        <v>2.302396882002506</v>
+        <v>2.302396882002592</v>
       </c>
       <c r="T6" t="n">
-        <v>2.096099240237502</v>
+        <v>2.096099240237592</v>
       </c>
       <c r="U6" t="n">
-        <v>3.636916560362196</v>
+        <v>3.636916560362287</v>
       </c>
       <c r="V6" t="n">
-        <v>2.61637775768815</v>
+        <v>2.616377757688138</v>
       </c>
       <c r="W6" t="n">
-        <v>4.872063569968033</v>
+        <v>4.872063569968169</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63522590893548</v>
+        <v>2.63522590893558</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.858864890292976</v>
+        <v>4.858864890293067</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.760157629752725</v>
+        <v>2.760157629752812</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.339225980265536</v>
+        <v>2.339225980265629</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.766344714976408</v>
+        <v>4.766344714976416</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3390611053771396</v>
+        <v>0.3390611053772541</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3659127473384599</v>
+        <v>0.3659127473384737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3354683447840371</v>
+        <v>0.3354683447840789</v>
       </c>
       <c r="F7" t="n">
-        <v>0.326644582225588</v>
+        <v>0.3266445822255884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3845561857757051</v>
+        <v>0.384556185775814</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3666692687714627</v>
+        <v>0.3666692687715061</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3905415857570092</v>
+        <v>0.3905415857570096</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3492641656166685</v>
+        <v>0.34926416561673</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3496357047019274</v>
+        <v>0.3496357047019263</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3472660613669953</v>
+        <v>0.3472660613670344</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3301427666418987</v>
+        <v>0.3301427666419894</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3529686372217088</v>
+        <v>0.3529686372218052</v>
       </c>
       <c r="V7" t="n">
-        <v>0.340978476066418</v>
+        <v>0.3409784760664035</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3751551253560463</v>
+        <v>0.3751551253561552</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3250064204502069</v>
+        <v>0.3250064204503392</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4295150839931119</v>
+        <v>0.4295150839931121</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3382181360130407</v>
+        <v>0.3382181360131508</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3844417821712867</v>
+        <v>0.3844417821713796</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4467111027288066</v>
+        <v>0.446711102728808</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.69148228385701</v>
+        <v>0.6914822838570064</v>
       </c>
       <c r="C2" t="n">
-        <v>1.160103562501217</v>
+        <v>1.16010356250121</v>
       </c>
       <c r="D2" t="n">
-        <v>1.781053574300565</v>
+        <v>1.781053574300571</v>
       </c>
       <c r="E2" t="n">
-        <v>2.412093412060388</v>
+        <v>2.412093412060401</v>
       </c>
       <c r="F2" t="n">
-        <v>2.007193625456828</v>
+        <v>2.007193625456834</v>
       </c>
       <c r="G2" t="n">
-        <v>6.911023047578635</v>
+        <v>6.911023047578603</v>
       </c>
       <c r="H2" t="n">
-        <v>5.596032060176712</v>
+        <v>5.596032060176698</v>
       </c>
       <c r="I2" t="n">
-        <v>1.522254049208686</v>
+        <v>1.52225404920871</v>
       </c>
       <c r="J2" t="n">
-        <v>5.140346601828362</v>
+        <v>5.140346601828075</v>
       </c>
       <c r="K2" t="n">
-        <v>3.013589939078743</v>
+        <v>3.013589939078744</v>
       </c>
       <c r="L2" t="n">
-        <v>3.039213464297057</v>
+        <v>3.039213464297053</v>
       </c>
       <c r="M2" t="n">
-        <v>4.98808061808367</v>
+        <v>4.988080618083669</v>
       </c>
       <c r="N2" t="n">
-        <v>5.350022311711388</v>
+        <v>5.350022311711386</v>
       </c>
       <c r="O2" t="n">
-        <v>6.297450168207788</v>
+        <v>6.297450168207797</v>
       </c>
       <c r="P2" t="n">
-        <v>8.641285231294024</v>
+        <v>8.641285231294018</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.772877813300018</v>
+        <v>2.772877813300024</v>
       </c>
       <c r="R2" t="n">
-        <v>1.807212955298935</v>
+        <v>1.807212955298936</v>
       </c>
       <c r="S2" t="n">
-        <v>2.820417227957754</v>
+        <v>2.820417227957749</v>
       </c>
       <c r="T2" t="n">
-        <v>3.584973100393976</v>
+        <v>3.5849731003939</v>
       </c>
       <c r="U2" t="n">
-        <v>5.409876404998481</v>
+        <v>5.409876404998483</v>
       </c>
       <c r="V2" t="n">
-        <v>4.424188728552588</v>
+        <v>4.424188728552581</v>
       </c>
       <c r="W2" t="n">
         <v>10.08834221100103</v>
       </c>
       <c r="X2" t="n">
-        <v>7.041692189466186</v>
+        <v>7.041692189466147</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.06989279130764</v>
+        <v>12.06989279130765</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.207518189854506</v>
+        <v>3.207518189854496</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.961687706759851</v>
+        <v>3.961687706759637</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.807635387361854</v>
+        <v>9.807635387361856</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3701131491164725</v>
+        <v>0.3701131491164741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4641306874561951</v>
+        <v>0.4641306874561948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4024389169273824</v>
+        <v>0.4024389169273863</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3755312048052405</v>
+        <v>0.3755312048052338</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4934696909556188</v>
+        <v>0.4934696909556317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4666813842071332</v>
+        <v>0.4666813842071391</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4686771763062548</v>
+        <v>0.4686771763062552</v>
       </c>
       <c r="N3" t="n">
         <v>0.3930844789928786</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4148491720817555</v>
+        <v>0.4148491720817467</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4095141199050149</v>
+        <v>0.4095141199050186</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3500342613879263</v>
+        <v>0.3500342613879285</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4220831883674117</v>
+        <v>0.422083188367423</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4305615811036748</v>
+        <v>0.430561581103668</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4723039960585062</v>
+        <v>0.4723039960585148</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3593984151645575</v>
+        <v>0.3593984151645563</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5733011057287889</v>
+        <v>0.5733011057287716</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.368215274666629</v>
+        <v>0.3682152746666319</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4722839167230025</v>
+        <v>0.4722839167230101</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5965028685255123</v>
+        <v>0.5965028685255072</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.616700726599017</v>
+        <v>9.616700726599037</v>
       </c>
       <c r="C4" t="n">
-        <v>9.782326206896844</v>
+        <v>9.782326206896775</v>
       </c>
       <c r="D4" t="n">
-        <v>10.01383666757364</v>
+        <v>10.01383666757361</v>
       </c>
       <c r="E4" t="n">
-        <v>10.23402965527137</v>
+        <v>10.23402965527135</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08958985105853</v>
+        <v>10.08958985105849</v>
       </c>
       <c r="G4" t="n">
-        <v>11.8836503014406</v>
+        <v>11.88365030144045</v>
       </c>
       <c r="H4" t="n">
-        <v>11.40435152793637</v>
+        <v>11.40435152793633</v>
       </c>
       <c r="I4" t="n">
-        <v>9.9195072796551</v>
+        <v>9.919507279655093</v>
       </c>
       <c r="J4" t="n">
-        <v>11.25205932291694</v>
+        <v>11.25205932291689</v>
       </c>
       <c r="K4" t="n">
         <v>10.46308169936257</v>
       </c>
       <c r="L4" t="n">
-        <v>10.47242117341802</v>
+        <v>10.47242117341797</v>
       </c>
       <c r="M4" t="n">
-        <v>11.1804682403323</v>
+        <v>11.18046824033222</v>
       </c>
       <c r="N4" t="n">
-        <v>11.31468386341308</v>
+        <v>11.31468386341309</v>
       </c>
       <c r="O4" t="n">
-        <v>11.66001019184643</v>
+        <v>11.66001019184639</v>
       </c>
       <c r="P4" t="n">
-        <v>12.51431054964049</v>
+        <v>12.51431054964051</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.37534495610071</v>
+        <v>10.37534495610069</v>
       </c>
       <c r="R4" t="n">
-        <v>10.02337145476858</v>
+        <v>10.02337145476857</v>
       </c>
       <c r="S4" t="n">
-        <v>10.39267251450747</v>
+        <v>10.39267251450746</v>
       </c>
       <c r="T4" t="n">
-        <v>10.67134415214214</v>
+        <v>10.67134415214211</v>
       </c>
       <c r="U4" t="n">
-        <v>11.33649997757397</v>
+        <v>11.33649997757396</v>
       </c>
       <c r="V4" t="n">
-        <v>11.08451750228352</v>
+        <v>11.08451750228351</v>
       </c>
       <c r="W4" t="n">
         <v>13.04174582654274</v>
       </c>
       <c r="X4" t="n">
-        <v>11.93127766926407</v>
+        <v>11.93127766926403</v>
       </c>
       <c r="Y4" t="n">
         <v>13.7639977445228</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.53376626954984</v>
+        <v>10.53376626954986</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.80865220255626</v>
+        <v>10.80865220255625</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.95054851902635</v>
+        <v>12.95054851902633</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.499565450693011</v>
+        <v>9.499565450693009</v>
       </c>
       <c r="C5" t="n">
-        <v>9.528652266469038</v>
+        <v>9.528652266469033</v>
       </c>
       <c r="D5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="E5" t="n">
-        <v>9.501534190349902</v>
+        <v>9.501534190349849</v>
       </c>
       <c r="F5" t="n">
-        <v>9.494868058678525</v>
+        <v>9.494868058678509</v>
       </c>
       <c r="G5" t="n">
-        <v>9.544527461667732</v>
+        <v>9.544527461667718</v>
       </c>
       <c r="H5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="I5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="J5" t="n">
-        <v>9.548563232041806</v>
+        <v>9.548563232041765</v>
       </c>
       <c r="K5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="L5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="M5" t="n">
-        <v>9.533198755319001</v>
+        <v>9.533198755318956</v>
       </c>
       <c r="N5" t="n">
-        <v>9.507938230689982</v>
+        <v>9.507938230689922</v>
       </c>
       <c r="O5" t="n">
-        <v>9.515871205746938</v>
+        <v>9.515871205746931</v>
       </c>
       <c r="P5" t="n">
-        <v>9.513926641875871</v>
+        <v>9.513926641875919</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.492246931894138</v>
+        <v>9.492246931894144</v>
       </c>
       <c r="R5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="S5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="T5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="U5" t="n">
-        <v>9.51850791973696</v>
+        <v>9.518507919737003</v>
       </c>
       <c r="V5" t="n">
-        <v>9.628887302576011</v>
+        <v>9.62888730257599</v>
       </c>
       <c r="W5" t="n">
-        <v>9.536812814417852</v>
+        <v>9.536812814417885</v>
       </c>
       <c r="X5" t="n">
-        <v>9.495660055986285</v>
+        <v>9.495660055986274</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.573625074924745</v>
+        <v>9.573625074924701</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.498873697741999</v>
+        <v>9.498873697741955</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.536805495735857</v>
+        <v>9.536805495735823</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.593198878489428</v>
+        <v>9.593198878489437</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3931793543673703</v>
+        <v>0.3931793543673656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5588048346651991</v>
+        <v>0.5588048346652006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7903152953419939</v>
+        <v>0.790315295341985</v>
       </c>
       <c r="E6" t="n">
-        <v>1.010508283039719</v>
+        <v>1.010508283039718</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8660684788268882</v>
+        <v>0.8660684788268866</v>
       </c>
       <c r="G6" t="n">
-        <v>2.65200740442084</v>
+        <v>2.652007404420833</v>
       </c>
       <c r="H6" t="n">
-        <v>2.180830155704727</v>
+        <v>2.180830155704721</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6959859074234594</v>
+        <v>0.6959859074234677</v>
       </c>
       <c r="J6" t="n">
-        <v>2.003354005730202</v>
+        <v>2.003354005730128</v>
       </c>
       <c r="K6" t="n">
         <v>1.239560327130925</v>
       </c>
       <c r="L6" t="n">
-        <v>1.248899801186376</v>
+        <v>1.248899801186378</v>
       </c>
       <c r="M6" t="n">
-        <v>1.956946868100642</v>
+        <v>1.956946868100648</v>
       </c>
       <c r="N6" t="n">
-        <v>2.091162491181432</v>
+        <v>2.091162491181433</v>
       </c>
       <c r="O6" t="n">
-        <v>2.428367294826675</v>
+        <v>2.428367294826679</v>
       </c>
       <c r="P6" t="n">
-        <v>3.282667652620737</v>
+        <v>3.28266765262074</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.15182358386907</v>
+        <v>1.151823583869065</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7998500825369395</v>
+        <v>0.7998500825369331</v>
       </c>
       <c r="S6" t="n">
-        <v>1.169151142275823</v>
+        <v>1.16915114227582</v>
       </c>
       <c r="T6" t="n">
-        <v>1.447822779910496</v>
+        <v>1.44782277991049</v>
       </c>
       <c r="U6" t="n">
-        <v>2.104857080554215</v>
+        <v>2.104857080554217</v>
       </c>
       <c r="V6" t="n">
         <v>1.73748256239138</v>
       </c>
       <c r="W6" t="n">
-        <v>3.810102929522985</v>
+        <v>3.810102929522988</v>
       </c>
       <c r="X6" t="n">
-        <v>2.699634772244322</v>
+        <v>2.699634772244292</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.540476372291163</v>
+        <v>4.540476372291161</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.310244897318198</v>
+        <v>1.310244897318199</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.585130830324614</v>
+        <v>1.585130830324593</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.7270271467947</v>
+        <v>3.727027146794707</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2760440784613542</v>
+        <v>0.2760440784613567</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3051308942373999</v>
+        <v>0.3051308942373892</v>
       </c>
       <c r="D7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.27801281811826</v>
+        <v>0.2780128181182615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2713466864468727</v>
+        <v>0.2713466864468684</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3128845646479642</v>
+        <v>0.3128845646479593</v>
       </c>
       <c r="H7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="I7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2998579148550742</v>
+        <v>0.2998579148550814</v>
       </c>
       <c r="K7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="L7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3096773830873544</v>
+        <v>0.3096773830873511</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2844168584583319</v>
+        <v>0.2844168584583264</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2842283087271837</v>
+        <v>0.2842283087271816</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2822837448561085</v>
+        <v>0.2822837448561079</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2687255596625019</v>
+        <v>0.268725559662503</v>
       </c>
       <c r="R7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="S7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="T7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2868650227171996</v>
+        <v>0.2868650227172053</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2818523626838716</v>
+        <v>0.2818523626838744</v>
       </c>
       <c r="W7" t="n">
         <v>0.3051699173981047</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2640171589665254</v>
+        <v>0.2640171589665257</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3501037026930962</v>
+        <v>0.3501037026931043</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2753523255103525</v>
+        <v>0.2753523255103515</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.31328412350421</v>
+        <v>0.3132841235042065</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3696775062577847</v>
+        <v>0.3696775062577962</v>
       </c>
     </row>
   </sheetData>
